--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_14_49.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_14_49.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6213408.384181429</v>
+        <v>6173382.29142803</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6767152.31864579</v>
+        <v>6767152.318645785</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6767152.31864579</v>
+        <v>6767152.318645785</v>
       </c>
     </row>
     <row r="9">
@@ -660,58 +660,58 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
-        <v>410.3391557398498</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
         <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>404.8896287080119</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
         <v>403.7573722870162</v>
       </c>
       <c r="H2" t="n">
-        <v>408.0096587035274</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>93.56939138541446</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>418.7382696589336</v>
+        <v>797.8013999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>97.12488247690061</v>
+        <v>97.12488247690055</v>
       </c>
       <c r="L2" t="n">
+        <v>31.55202437320317</v>
+      </c>
+      <c r="M2" t="n">
+        <v>297.9910820919849</v>
+      </c>
+      <c r="N2" t="n">
         <v>814</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>814</v>
-      </c>
-      <c r="N2" t="n">
-        <v>708.6062368062543</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>370.9706110579117</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T2" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U2" t="n">
-        <v>249.2212965486107</v>
+        <v>491.9120891057307</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -736,25 +736,25 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>175.4172848236331</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>170.8861760628761</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -842,10 +842,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
-        <v>114.9691617061026</v>
+        <v>120.6316114025499</v>
       </c>
       <c r="N4" t="n">
         <v>171.1850752716849</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>326.6021279811511</v>
+        <v>297.3920501269264</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>81.99931295557451</v>
+        <v>425.4875446583037</v>
       </c>
       <c r="C5" t="n">
-        <v>449.4745782429939</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
         <v>10.33915573984979</v>
@@ -915,25 +915,25 @@
         <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
-        <v>418.7382696589336</v>
+        <v>797.8013999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>507.7400371911698</v>
+        <v>97.12488247690055</v>
       </c>
       <c r="L5" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>297.9910820919849</v>
       </c>
       <c r="N5" t="n">
+        <v>194.5855355810472</v>
+      </c>
+      <c r="O5" t="n">
+        <v>650.9664887921559</v>
+      </c>
+      <c r="P5" t="n">
         <v>814</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>370.9706110579117</v>
@@ -945,7 +945,7 @@
         <v>494.8481678023229</v>
       </c>
       <c r="T5" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U5" t="n">
         <v>249.2212965486107</v>
@@ -960,7 +960,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
-        <v>454.8056643855364</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="6">
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>73.16906773709616</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1030,13 +1030,13 @@
         <v>0.2103597601867477</v>
       </c>
       <c r="V6" t="n">
-        <v>87.67973492861624</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>432.3731429098285</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>19.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>120.6316114025499</v>
+        <v>114.9691617060907</v>
       </c>
       <c r="N7" t="n">
         <v>171.1850752716849</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>320.9396782847081</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81.99931295557451</v>
+        <v>481.9993129555745</v>
       </c>
       <c r="C8" t="n">
         <v>49.47457824299391</v>
@@ -1143,19 +1143,19 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>403.7573722870162</v>
+        <v>246.4481648441365</v>
       </c>
       <c r="H8" t="n">
         <v>408.0096587035274</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>418.7382696589336</v>
       </c>
       <c r="K8" t="n">
-        <v>313.154501610127</v>
+        <v>97.12488247690061</v>
       </c>
       <c r="L8" t="n">
         <v>814</v>
@@ -1173,7 +1173,7 @@
         <v>814</v>
       </c>
       <c r="Q8" t="n">
-        <v>370.9706110579117</v>
+        <v>587.0002301911378</v>
       </c>
       <c r="R8" t="n">
         <v>250.8785988282945</v>
@@ -1182,10 +1182,10 @@
         <v>94.84816780232291</v>
       </c>
       <c r="T8" t="n">
-        <v>279.2852146029995</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U8" t="n">
-        <v>649.2212965486107</v>
+        <v>249.2212965486107</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1255,13 +1255,13 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>547.2737972923793</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S9" t="n">
-        <v>466.5639999646113</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>63.08338960093663</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
         <v>0.2103597601867477</v>
@@ -1273,10 +1273,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>93.64041441634932</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -1316,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>120.6316114025499</v>
+        <v>114.9691617061071</v>
       </c>
       <c r="N10" t="n">
         <v>171.1850752716849</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>297.3920501269242</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1374,16 +1374,16 @@
         <v>185.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>50.65334830746261</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1413,10 +1413,10 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
-        <v>234.4375084931612</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T11" t="n">
         <v>361.6755817285639</v>
@@ -1431,10 +1431,10 @@
         <v>413.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>367.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>286.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="Q13" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>159.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>153.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>153.8896287080119</v>
+        <v>67.57968198731129</v>
       </c>
       <c r="G14" t="n">
-        <v>152.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>8.427217891264409</v>
+        <v>243.8481678023229</v>
       </c>
       <c r="T14" t="n">
         <v>335.6755817285639</v>
@@ -1799,16 +1799,16 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>92.1326498274306</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q16" t="n">
-        <v>52.97841917455702</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>475.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>9.520773801143037</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2042,13 +2042,13 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>338.6387678008247</v>
+        <v>4.112902894276309</v>
       </c>
       <c r="R19" t="n">
         <v>447.6021279811511</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2279,13 +2279,13 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>446.839266425598</v>
+        <v>255.2652880979692</v>
       </c>
       <c r="R22" t="n">
-        <v>339.4016293563777</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2322,7 +2322,7 @@
         <v>131.3391557398498</v>
       </c>
       <c r="E23" t="n">
-        <v>124.9326809922826</v>
+        <v>125.3632896068686</v>
       </c>
       <c r="F23" t="n">
         <v>125.8896287080119</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>215.8481678023229</v>
+        <v>215.4175591877372</v>
       </c>
       <c r="T23" t="n">
         <v>307.6755817285639</v>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>377.7929984536983</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>339.4016293563777</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2550,16 +2550,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>221.9364105579686</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
         <v>224.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>49.4461096648668</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S26" t="n">
-        <v>269.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>361.6755817285639</v>
@@ -2735,16 +2735,16 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>63.52077380114304</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>139.8825459845292</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2759,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2787,25 +2787,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>256.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>224.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>174.6024969047295</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2835,10 +2835,10 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S29" t="n">
-        <v>75.324708493161</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>361.6755817285639</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="R31" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>190.9993129555745</v>
+        <v>199.4559043409888</v>
       </c>
       <c r="C32" t="n">
         <v>158.4745782429939</v>
@@ -3048,31 +3048,31 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>377.7382696589747</v>
+        <v>377.7382696589756</v>
       </c>
       <c r="K32" t="n">
-        <v>10.23281455295068</v>
+        <v>10.23281455321944</v>
       </c>
       <c r="L32" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>256.9910820920259</v>
+        <v>256.9910820920268</v>
       </c>
       <c r="N32" t="n">
-        <v>773.0000000000412</v>
+        <v>153.5855355810893</v>
       </c>
       <c r="O32" t="n">
-        <v>495.1684068660326</v>
+        <v>702.3188823428534</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="Q32" t="n">
-        <v>329.9706110579529</v>
+        <v>742.2346000000399</v>
       </c>
       <c r="R32" t="n">
-        <v>8.456591385414804</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>203.8481678023229</v>
@@ -3212,19 +3212,19 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>81.229674441146</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>229.6316114025499</v>
+        <v>62.05083562934757</v>
       </c>
       <c r="N34" t="n">
-        <v>280.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>349.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -3282,31 +3282,31 @@
         <v>117.0096587035274</v>
       </c>
       <c r="I35" t="n">
-        <v>8.45659138541424</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>377.738269658982</v>
+        <v>377.7382696589829</v>
       </c>
       <c r="K35" t="n">
-        <v>10.23281455318585</v>
+        <v>56.12488247690044</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>727.1079320760183</v>
       </c>
       <c r="M35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="N35" t="n">
-        <v>773.0000000000484</v>
+        <v>752.1594889580832</v>
       </c>
       <c r="O35" t="n">
-        <v>752.1594889580271</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>329.9706110579601</v>
+        <v>329.970611057961</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3330,7 +3330,7 @@
         <v>301.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>220.3174326828064</v>
+        <v>228.7740240682207</v>
       </c>
     </row>
     <row r="36">
@@ -3455,13 +3455,13 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>70.05053078764654</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>70.05053078766994</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>434.839266425598</v>
@@ -3522,19 +3522,19 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>757.6173000000546</v>
+        <v>757.6173000000554</v>
       </c>
       <c r="K38" t="n">
-        <v>10.23281455286669</v>
+        <v>10.23281455315785</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="M38" t="n">
-        <v>717.6337696749497</v>
+        <v>256.9910820920413</v>
       </c>
       <c r="N38" t="n">
-        <v>773.0000000000557</v>
+        <v>460.642687582962</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -3543,10 +3543,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>757.6173000000545</v>
+        <v>757.6173000000553</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>8.456591385414804</v>
       </c>
       <c r="S38" t="n">
         <v>203.8481678023229</v>
@@ -3567,7 +3567,7 @@
         <v>301.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>228.7740240682207</v>
+        <v>220.3174326828064</v>
       </c>
     </row>
     <row r="39">
@@ -3695,13 +3695,13 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>108.4418998849941</v>
       </c>
       <c r="P40" t="n">
-        <v>70.05053078764654</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q40" t="n">
-        <v>434.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>435.6021279811511</v>
@@ -3738,16 +3738,16 @@
         <v>268.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>236.4745782429939</v>
       </c>
       <c r="D41" t="n">
         <v>197.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>191.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>191.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -3795,16 +3795,16 @@
         <v>436.2212965486107</v>
       </c>
       <c r="V41" t="n">
-        <v>148.0344432349017</v>
+        <v>416.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>425.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>379.2818334606677</v>
+        <v>130.1875493024912</v>
       </c>
       <c r="Y41" t="n">
-        <v>298.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>334.2737972923793</v>
+        <v>50.78614729240174</v>
       </c>
       <c r="S42" t="n">
         <v>253.5639999646113</v>
@@ -3877,7 +3877,7 @@
         <v>201.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>81.90670016750896</v>
+        <v>219.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>206.8627394453875</v>
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>257.9707994885276</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -3972,13 +3972,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>69.78894098820233</v>
+        <v>294.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>262.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>223.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -3987,10 +3987,10 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>111.0369929792993</v>
       </c>
       <c r="H44" t="n">
-        <v>221.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4023,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>307.8481678023229</v>
       </c>
       <c r="T44" t="n">
         <v>399.6755817285639</v>
       </c>
       <c r="U44" t="n">
-        <v>462.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>442.8510241668239</v>
@@ -4054,7 +4054,7 @@
         <v>197.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>11.13598278058154</v>
+        <v>174.0999124455193</v>
       </c>
       <c r="D45" t="n">
         <v>160.9376868977026</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>62.48758491141504</v>
       </c>
       <c r="T45" t="n">
         <v>218.3577652175138</v>
@@ -4114,7 +4114,7 @@
         <v>227.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>245.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>232.8627394453875</v>
@@ -4184,13 +4184,13 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>23.02456650625771</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>12.17031021621619</v>
       </c>
       <c r="W46" t="n">
         <v>0</v>
@@ -4297,46 +4297,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1857.446338054225</v>
+        <v>550.8105891800685</v>
       </c>
       <c r="C2" t="n">
-        <v>1807.472016596655</v>
+        <v>500.8362677224989</v>
       </c>
       <c r="D2" t="n">
-        <v>1392.988020899837</v>
+        <v>490.392676066085</v>
       </c>
       <c r="E2" t="n">
-        <v>1388.580657660576</v>
+        <v>485.9853128268238</v>
       </c>
       <c r="F2" t="n">
-        <v>979.60123472319</v>
+        <v>481.0462939298421</v>
       </c>
       <c r="G2" t="n">
-        <v>571.7655051403453</v>
+        <v>73.21056434699739</v>
       </c>
       <c r="H2" t="n">
-        <v>159.6345367529439</v>
+        <v>65.12</v>
       </c>
       <c r="I2" t="n">
         <v>65.12</v>
       </c>
       <c r="J2" t="n">
-        <v>448.0120508495621</v>
+        <v>65.12</v>
       </c>
       <c r="K2" t="n">
-        <v>1155.766108953703</v>
+        <v>772.8740581041409</v>
       </c>
       <c r="L2" t="n">
-        <v>1139.40388673148</v>
+        <v>1546.863326414037</v>
       </c>
       <c r="M2" t="n">
-        <v>1123.041664509258</v>
+        <v>2051.72223339183</v>
       </c>
       <c r="N2" t="n">
-        <v>1213.137788947385</v>
+        <v>2035.360011169607</v>
       </c>
       <c r="O2" t="n">
-        <v>2018.997788947385</v>
+        <v>2841.220011169607</v>
       </c>
       <c r="P2" t="n">
         <v>2824.857788947385</v>
@@ -4345,28 +4345,28 @@
         <v>3256</v>
       </c>
       <c r="R2" t="n">
-        <v>3256</v>
+        <v>3002.587273910814</v>
       </c>
       <c r="S2" t="n">
-        <v>3160.193769896644</v>
+        <v>2502.740639767053</v>
       </c>
       <c r="T2" t="n">
-        <v>2971.632576231427</v>
+        <v>1910.139042061433</v>
       </c>
       <c r="U2" t="n">
-        <v>2719.893892848992</v>
+        <v>1413.258143974836</v>
       </c>
       <c r="V2" t="n">
-        <v>2487.721141165332</v>
+        <v>1181.085392291176</v>
       </c>
       <c r="W2" t="n">
-        <v>2246.939852295688</v>
+        <v>940.3041034215316</v>
       </c>
       <c r="X2" t="n">
-        <v>2052.715778092993</v>
+        <v>746.080029218837</v>
       </c>
       <c r="Y2" t="n">
-        <v>1940.273926898239</v>
+        <v>633.6381780240831</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>758.8972205258048</v>
+        <v>2966.957099210679</v>
       </c>
       <c r="C3" t="n">
-        <v>394.1498342171994</v>
+        <v>2966.957099210679</v>
       </c>
       <c r="D3" t="n">
-        <v>394.1498342171994</v>
+        <v>2966.957099210679</v>
       </c>
       <c r="E3" t="n">
-        <v>394.1498342171994</v>
+        <v>2620.823667673394</v>
       </c>
       <c r="F3" t="n">
-        <v>394.1498342171994</v>
+        <v>2277.756756220993</v>
       </c>
       <c r="G3" t="n">
-        <v>65.12</v>
+        <v>2277.756756220993</v>
       </c>
       <c r="H3" t="n">
-        <v>65.12</v>
+        <v>2277.756756220993</v>
       </c>
       <c r="I3" t="n">
-        <v>65.12</v>
+        <v>2100.567579631464</v>
       </c>
       <c r="J3" t="n">
-        <v>189.076520175299</v>
+        <v>2224.524099806763</v>
       </c>
       <c r="K3" t="n">
-        <v>378.2693362696824</v>
+        <v>2413.716915901147</v>
       </c>
       <c r="L3" t="n">
-        <v>649.6197978648825</v>
+        <v>2685.067377496347</v>
       </c>
       <c r="M3" t="n">
-        <v>735.7003396077417</v>
+        <v>2771.147919239206</v>
       </c>
       <c r="N3" t="n">
-        <v>868.9806242153101</v>
+        <v>2904.428203846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1108.023075899029</v>
+        <v>3143.470655530493</v>
       </c>
       <c r="P3" t="n">
-        <v>1220.552420368536</v>
+        <v>3256</v>
       </c>
       <c r="Q3" t="n">
-        <v>1047.940121315125</v>
+        <v>3256</v>
       </c>
       <c r="R3" t="n">
-        <v>899.1787099086816</v>
+        <v>3107.238588593556</v>
       </c>
       <c r="S3" t="n">
-        <v>831.9423463080642</v>
+        <v>3040.002224992939</v>
       </c>
       <c r="T3" t="n">
-        <v>826.5304622499694</v>
+        <v>3034.590340934844</v>
       </c>
       <c r="U3" t="n">
-        <v>826.3179776437202</v>
+        <v>3034.377856328595</v>
       </c>
       <c r="V3" t="n">
-        <v>811.6607380563261</v>
+        <v>3019.720616741201</v>
       </c>
       <c r="W3" t="n">
-        <v>778.9605937029639</v>
+        <v>2987.020472387838</v>
       </c>
       <c r="X3" t="n">
-        <v>758.8972205258048</v>
+        <v>2966.957099210679</v>
       </c>
       <c r="Y3" t="n">
-        <v>758.8972205258048</v>
+        <v>2966.957099210679</v>
       </c>
     </row>
     <row r="4">
@@ -4464,43 +4464,43 @@
         <v>851.0307263663814</v>
       </c>
       <c r="E4" t="n">
-        <v>937.1572625793682</v>
+        <v>968.8596305777944</v>
       </c>
       <c r="F4" t="n">
-        <v>1061.518235171304</v>
+        <v>1093.22060316973</v>
       </c>
       <c r="G4" t="n">
-        <v>1214.924801058189</v>
+        <v>1246.627169056615</v>
       </c>
       <c r="H4" t="n">
-        <v>1214.924801058189</v>
+        <v>1416.143754216013</v>
       </c>
       <c r="I4" t="n">
-        <v>1436.057679994272</v>
+        <v>1436.057679994274</v>
       </c>
       <c r="J4" t="n">
-        <v>1436.057679994272</v>
+        <v>1436.057679994274</v>
       </c>
       <c r="K4" t="n">
-        <v>1546.422113931141</v>
+        <v>1546.422113931143</v>
       </c>
       <c r="L4" t="n">
-        <v>1546.422113931141</v>
+        <v>1522.636630943487</v>
       </c>
       <c r="M4" t="n">
-        <v>1430.29164756134</v>
+        <v>1400.786518415659</v>
       </c>
       <c r="N4" t="n">
-        <v>1257.377430115193</v>
+        <v>1227.872300969512</v>
       </c>
       <c r="O4" t="n">
-        <v>1014.503122964673</v>
+        <v>984.9979938189919</v>
       </c>
       <c r="P4" t="n">
-        <v>724.1517115219688</v>
+        <v>694.6465823762874</v>
       </c>
       <c r="Q4" t="n">
-        <v>395.0211393749001</v>
+        <v>365.5160102292186</v>
       </c>
       <c r="R4" t="n">
         <v>65.12</v>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1106.448124213083</v>
+        <v>702.4077201726793</v>
       </c>
       <c r="C5" t="n">
         <v>652.4333987151097</v>
@@ -4558,22 +4558,22 @@
         <v>65.12</v>
       </c>
       <c r="J5" t="n">
-        <v>448.0120508495621</v>
+        <v>65.12</v>
       </c>
       <c r="K5" t="n">
-        <v>741.0033264140369</v>
+        <v>772.8740581041409</v>
       </c>
       <c r="L5" t="n">
-        <v>724.6411041918145</v>
+        <v>1578.734058104141</v>
       </c>
       <c r="M5" t="n">
-        <v>1229.500011169607</v>
+        <v>2083.592965081934</v>
       </c>
       <c r="N5" t="n">
-        <v>1213.137788947385</v>
+        <v>2692.901919040472</v>
       </c>
       <c r="O5" t="n">
-        <v>2018.997788947385</v>
+        <v>2841.220011169607</v>
       </c>
       <c r="P5" t="n">
         <v>2824.857788947385</v>
@@ -4588,22 +4588,22 @@
         <v>2756.153365856239</v>
       </c>
       <c r="T5" t="n">
-        <v>2567.592172191023</v>
+        <v>2163.551768150619</v>
       </c>
       <c r="U5" t="n">
-        <v>2315.853488808588</v>
+        <v>1911.813084768184</v>
       </c>
       <c r="V5" t="n">
-        <v>2083.680737124928</v>
+        <v>1679.640333084523</v>
       </c>
       <c r="W5" t="n">
-        <v>1842.899448255284</v>
+        <v>1438.859044214879</v>
       </c>
       <c r="X5" t="n">
-        <v>1648.675374052589</v>
+        <v>1244.634970012185</v>
       </c>
       <c r="Y5" t="n">
-        <v>1189.275713057098</v>
+        <v>1132.193118817431</v>
       </c>
     </row>
     <row r="6">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65.12</v>
+        <v>139.0281492293901</v>
       </c>
       <c r="C6" t="n">
-        <v>65.12</v>
+        <v>139.0281492293901</v>
       </c>
       <c r="D6" t="n">
         <v>65.12</v>
@@ -4673,16 +4673,16 @@
         <v>998.9302766971304</v>
       </c>
       <c r="V6" t="n">
-        <v>910.3648878803463</v>
+        <v>984.2730371097363</v>
       </c>
       <c r="W6" t="n">
-        <v>473.62433948658</v>
+        <v>951.5728927563741</v>
       </c>
       <c r="X6" t="n">
-        <v>453.5609663094208</v>
+        <v>527.4691155388109</v>
       </c>
       <c r="Y6" t="n">
-        <v>453.5609663094208</v>
+        <v>527.4691155388109</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>857.759540267482</v>
+        <v>601.024664805216</v>
       </c>
       <c r="C7" t="n">
-        <v>983.7615460859178</v>
+        <v>727.0266706236519</v>
       </c>
       <c r="D7" t="n">
-        <v>1097.080690210918</v>
+        <v>840.3458147486519</v>
       </c>
       <c r="E7" t="n">
-        <v>1200.928262403127</v>
+        <v>921.0472433068438</v>
       </c>
       <c r="F7" t="n">
-        <v>1325.289234995062</v>
+        <v>1045.408215898779</v>
       </c>
       <c r="G7" t="n">
-        <v>1325.289234995062</v>
+        <v>1045.408215898779</v>
       </c>
       <c r="H7" t="n">
-        <v>1325.289234995062</v>
+        <v>1214.924801058177</v>
       </c>
       <c r="I7" t="n">
-        <v>1546.422113931145</v>
+        <v>1436.05767999426</v>
       </c>
       <c r="J7" t="n">
-        <v>1546.422113931145</v>
+        <v>1436.05767999426</v>
       </c>
       <c r="K7" t="n">
-        <v>1546.422113931145</v>
+        <v>1546.422113931128</v>
       </c>
       <c r="L7" t="n">
-        <v>1546.422113931145</v>
+        <v>1546.422113931128</v>
       </c>
       <c r="M7" t="n">
-        <v>1424.572001403317</v>
+        <v>1430.29164756134</v>
       </c>
       <c r="N7" t="n">
-        <v>1251.65778395717</v>
+        <v>1257.377430115193</v>
       </c>
       <c r="O7" t="n">
-        <v>1008.78347680665</v>
+        <v>1014.503122964673</v>
       </c>
       <c r="P7" t="n">
-        <v>718.4320653639456</v>
+        <v>724.1517115219688</v>
       </c>
       <c r="Q7" t="n">
-        <v>389.3014932168769</v>
+        <v>395.0211393749001</v>
       </c>
       <c r="R7" t="n">
         <v>65.12</v>
       </c>
       <c r="S7" t="n">
-        <v>65.12</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="T7" t="n">
-        <v>65.12</v>
+        <v>290.445934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>311.6711926382866</v>
+        <v>290.445934252978</v>
       </c>
       <c r="V7" t="n">
-        <v>311.6711926382866</v>
+        <v>489.2673271389239</v>
       </c>
       <c r="W7" t="n">
-        <v>483.5621108979641</v>
+        <v>489.2673271389239</v>
       </c>
       <c r="X7" t="n">
-        <v>634.5929019221576</v>
+        <v>489.2673271389239</v>
       </c>
       <c r="Y7" t="n">
-        <v>746.0022026011899</v>
+        <v>489.2673271389239</v>
       </c>
     </row>
     <row r="8">
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1106.448124213083</v>
+        <v>795.9528038842304</v>
       </c>
       <c r="C8" t="n">
-        <v>1056.473802755514</v>
+        <v>745.9784824266608</v>
       </c>
       <c r="D8" t="n">
-        <v>1046.0302110991</v>
+        <v>735.5348907702469</v>
       </c>
       <c r="E8" t="n">
-        <v>1041.622847859838</v>
+        <v>731.1275275309856</v>
       </c>
       <c r="F8" t="n">
-        <v>1036.683828962857</v>
+        <v>726.1885086340039</v>
       </c>
       <c r="G8" t="n">
-        <v>628.8480993800122</v>
+        <v>477.2509683874014</v>
       </c>
       <c r="H8" t="n">
-        <v>216.7171309926107</v>
+        <v>65.12</v>
       </c>
       <c r="I8" t="n">
         <v>65.12</v>
@@ -4798,22 +4798,22 @@
         <v>448.0120508495621</v>
       </c>
       <c r="K8" t="n">
-        <v>937.5543724554943</v>
+        <v>1155.766108953703</v>
       </c>
       <c r="L8" t="n">
-        <v>921.1921502332721</v>
+        <v>1139.40388673148</v>
       </c>
       <c r="M8" t="n">
-        <v>1426.051057211065</v>
+        <v>1644.262793709273</v>
       </c>
       <c r="N8" t="n">
-        <v>2035.360011169603</v>
+        <v>2253.571747667811</v>
       </c>
       <c r="O8" t="n">
-        <v>2841.220011169603</v>
+        <v>3059.431747667812</v>
       </c>
       <c r="P8" t="n">
-        <v>2824.857788947385</v>
+        <v>3043.069525445594</v>
       </c>
       <c r="Q8" t="n">
         <v>3256</v>
@@ -4825,22 +4825,22 @@
         <v>2906.781043807457</v>
       </c>
       <c r="T8" t="n">
-        <v>2624.67476643069</v>
+        <v>2314.179446101837</v>
       </c>
       <c r="U8" t="n">
-        <v>1968.895679007851</v>
+        <v>2062.440762719402</v>
       </c>
       <c r="V8" t="n">
-        <v>1736.722927324191</v>
+        <v>1830.268011035742</v>
       </c>
       <c r="W8" t="n">
-        <v>1495.941638454547</v>
+        <v>1589.486722166098</v>
       </c>
       <c r="X8" t="n">
-        <v>1301.717564251852</v>
+        <v>1395.262647963403</v>
       </c>
       <c r="Y8" t="n">
-        <v>1189.275713057098</v>
+        <v>1282.820796768649</v>
       </c>
     </row>
     <row r="9">
@@ -4898,28 +4898,28 @@
         <v>1220.552420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>667.7506049216878</v>
+        <v>1071.791008962092</v>
       </c>
       <c r="S9" t="n">
-        <v>196.4738372806663</v>
+        <v>1004.554645361474</v>
       </c>
       <c r="T9" t="n">
-        <v>132.7532417241646</v>
+        <v>999.1427613033796</v>
       </c>
       <c r="U9" t="n">
-        <v>132.5407571179154</v>
+        <v>998.9302766971304</v>
       </c>
       <c r="V9" t="n">
-        <v>117.8835175305213</v>
+        <v>984.2730371097363</v>
       </c>
       <c r="W9" t="n">
-        <v>85.18337317715914</v>
+        <v>951.5728927563741</v>
       </c>
       <c r="X9" t="n">
-        <v>65.12</v>
+        <v>856.9866155681425</v>
       </c>
       <c r="Y9" t="n">
-        <v>65.12</v>
+        <v>453.5609663094208</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>857.7747469033402</v>
+        <v>892.0016500119107</v>
       </c>
       <c r="C10" t="n">
-        <v>983.776752721776</v>
+        <v>892.0016500119107</v>
       </c>
       <c r="D10" t="n">
-        <v>1097.095896846776</v>
+        <v>892.0016500119107</v>
       </c>
       <c r="E10" t="n">
-        <v>1214.924801058189</v>
+        <v>892.0016500119107</v>
       </c>
       <c r="F10" t="n">
-        <v>1214.924801058189</v>
+        <v>892.0016500119107</v>
       </c>
       <c r="G10" t="n">
-        <v>1214.924801058189</v>
+        <v>1045.408215898796</v>
       </c>
       <c r="H10" t="n">
-        <v>1214.924801058189</v>
+        <v>1214.924801058194</v>
       </c>
       <c r="I10" t="n">
-        <v>1436.057679994272</v>
+        <v>1436.057679994277</v>
       </c>
       <c r="J10" t="n">
-        <v>1436.057679994272</v>
+        <v>1436.057679994277</v>
       </c>
       <c r="K10" t="n">
-        <v>1546.42211393114</v>
+        <v>1546.422113931145</v>
       </c>
       <c r="L10" t="n">
-        <v>1522.636630943485</v>
+        <v>1546.422113931145</v>
       </c>
       <c r="M10" t="n">
-        <v>1400.786518415656</v>
+        <v>1430.29164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1227.87230096951</v>
+        <v>1257.377430115193</v>
       </c>
       <c r="O10" t="n">
-        <v>984.9979938189896</v>
+        <v>1014.503122964673</v>
       </c>
       <c r="P10" t="n">
-        <v>694.6465823762851</v>
+        <v>724.1517115219688</v>
       </c>
       <c r="Q10" t="n">
-        <v>365.5160102292164</v>
+        <v>395.0211393749001</v>
       </c>
       <c r="R10" t="n">
         <v>65.12</v>
       </c>
       <c r="S10" t="n">
-        <v>102.3702550941731</v>
+        <v>86.66246706919578</v>
       </c>
       <c r="T10" t="n">
-        <v>290.445934252978</v>
+        <v>274.7381462280006</v>
       </c>
       <c r="U10" t="n">
-        <v>536.9971268912645</v>
+        <v>521.2893388662873</v>
       </c>
       <c r="V10" t="n">
-        <v>594.9866182128545</v>
+        <v>720.1107317522333</v>
       </c>
       <c r="W10" t="n">
-        <v>594.9866182128545</v>
+        <v>892.0016500119107</v>
       </c>
       <c r="X10" t="n">
-        <v>746.017409237048</v>
+        <v>892.0016500119107</v>
       </c>
       <c r="Y10" t="n">
-        <v>746.017409237048</v>
+        <v>892.0016500119107</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>479.0732666493371</v>
+        <v>1077.366204029153</v>
       </c>
       <c r="C11" t="n">
-        <v>252.3312684240907</v>
+        <v>850.624205803907</v>
       </c>
       <c r="D11" t="n">
-        <v>65.12</v>
+        <v>663.4129373798163</v>
       </c>
       <c r="E11" t="n">
-        <v>65.12</v>
+        <v>612.24793908945</v>
       </c>
       <c r="F11" t="n">
-        <v>65.12</v>
+        <v>430.5412434247916</v>
       </c>
       <c r="G11" t="n">
-        <v>65.12</v>
+        <v>249.9782411146742</v>
       </c>
       <c r="H11" t="n">
         <v>65.12</v>
@@ -5035,49 +5035,49 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>1166.135479385524</v>
+        <v>694.8320762183973</v>
       </c>
       <c r="L11" t="n">
-        <v>1971.995479385524</v>
+        <v>1500.692076218397</v>
       </c>
       <c r="M11" t="n">
-        <v>2482.844308114459</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="N11" t="n">
-        <v>3096.064627889222</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="O11" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>3256</v>
       </c>
       <c r="R11" t="n">
-        <v>3256</v>
+        <v>3229.860001183541</v>
       </c>
       <c r="S11" t="n">
-        <v>3019.194435865494</v>
+        <v>2957.286094312508</v>
       </c>
       <c r="T11" t="n">
-        <v>2653.865565432601</v>
+        <v>2591.957223879615</v>
       </c>
       <c r="U11" t="n">
-        <v>2225.359205282489</v>
+        <v>2163.450863729503</v>
       </c>
       <c r="V11" t="n">
-        <v>1816.418776831151</v>
+        <v>1754.510435278166</v>
       </c>
       <c r="W11" t="n">
-        <v>1398.869811193831</v>
+        <v>1336.961469640845</v>
       </c>
       <c r="X11" t="n">
-        <v>1027.878060223459</v>
+        <v>1336.961469640845</v>
       </c>
       <c r="Y11" t="n">
-        <v>738.6685322610285</v>
+        <v>1336.961469640845</v>
       </c>
     </row>
     <row r="12">
@@ -5111,19 +5111,19 @@
         <v>72.91487796756496</v>
       </c>
       <c r="J12" t="n">
-        <v>215.7971006891144</v>
+        <v>419.6213981428639</v>
       </c>
       <c r="K12" t="n">
-        <v>627.7399167834978</v>
+        <v>831.5642142372474</v>
       </c>
       <c r="L12" t="n">
-        <v>1121.840378378698</v>
+        <v>1325.664675832448</v>
       </c>
       <c r="M12" t="n">
-        <v>1430.670920121557</v>
+        <v>1634.495217575307</v>
       </c>
       <c r="N12" t="n">
-        <v>1786.701204729125</v>
+        <v>1990.525502182875</v>
       </c>
       <c r="O12" t="n">
         <v>2248.493656412844</v>
@@ -5208,7 +5208,7 @@
         <v>409.3389893823512</v>
       </c>
       <c r="P13" t="n">
-        <v>409.3389893823512</v>
+        <v>65.12</v>
       </c>
       <c r="Q13" t="n">
         <v>65.12</v>
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>891.2048733179198</v>
+        <v>653.4059340138207</v>
       </c>
       <c r="C14" t="n">
-        <v>690.7255013552997</v>
+        <v>452.9265620512006</v>
       </c>
       <c r="D14" t="n">
-        <v>529.7768591938352</v>
+        <v>291.9779198897361</v>
       </c>
       <c r="E14" t="n">
-        <v>374.8644454495234</v>
+        <v>291.9779198897361</v>
       </c>
       <c r="F14" t="n">
-        <v>219.4203760474911</v>
+        <v>223.7156148520479</v>
       </c>
       <c r="G14" t="n">
-        <v>65.12</v>
+        <v>223.7156148520479</v>
       </c>
       <c r="H14" t="n">
         <v>65.12</v>
@@ -5269,25 +5269,25 @@
         <v>65.12</v>
       </c>
       <c r="J14" t="n">
-        <v>456.4291130376557</v>
+        <v>177.7653900957659</v>
       </c>
       <c r="K14" t="n">
-        <v>1166.135479385524</v>
+        <v>887.4717564436343</v>
       </c>
       <c r="L14" t="n">
-        <v>1166.135479385524</v>
+        <v>887.4717564436343</v>
       </c>
       <c r="M14" t="n">
-        <v>1676.984308114459</v>
+        <v>1398.320585172569</v>
       </c>
       <c r="N14" t="n">
-        <v>2290.204627889222</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="O14" t="n">
-        <v>3096.064627889222</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P14" t="n">
-        <v>3096.064627889222</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="Q14" t="n">
         <v>3256</v>
@@ -5296,25 +5296,25 @@
         <v>3256</v>
       </c>
       <c r="S14" t="n">
-        <v>3247.487658695693</v>
+        <v>3009.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>2908.421414525426</v>
+        <v>2670.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>2506.17768063794</v>
+        <v>2268.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>2123.499878449229</v>
+        <v>1885.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>1732.213539074535</v>
+        <v>1494.414599770435</v>
       </c>
       <c r="X14" t="n">
-        <v>1387.48441436679</v>
+        <v>1149.68547506269</v>
       </c>
       <c r="Y14" t="n">
-        <v>1124.537512666985</v>
+        <v>886.7385733628859</v>
       </c>
     </row>
     <row r="15">
@@ -5345,28 +5345,28 @@
         <v>65.12</v>
       </c>
       <c r="I15" t="n">
-        <v>98.65487796756496</v>
+        <v>65.12</v>
       </c>
       <c r="J15" t="n">
-        <v>471.1013981428639</v>
+        <v>189.076520175299</v>
       </c>
       <c r="K15" t="n">
-        <v>908.7842142372473</v>
+        <v>378.2693362696824</v>
       </c>
       <c r="L15" t="n">
-        <v>1344.670984439304</v>
+        <v>649.6197978648825</v>
       </c>
       <c r="M15" t="n">
-        <v>1679.241526182163</v>
+        <v>984.1903396077416</v>
       </c>
       <c r="N15" t="n">
-        <v>1812.521810789732</v>
+        <v>1365.96062421531</v>
       </c>
       <c r="O15" t="n">
-        <v>2051.564262473451</v>
+        <v>1853.493075899029</v>
       </c>
       <c r="P15" t="n">
-        <v>2164.093606942957</v>
+        <v>2214.512420368535</v>
       </c>
       <c r="Q15" t="n">
         <v>2241.235134503383</v>
@@ -5442,13 +5442,13 @@
         <v>599.0397446017254</v>
       </c>
       <c r="O16" t="n">
-        <v>599.0397446017254</v>
+        <v>505.9764619477551</v>
       </c>
       <c r="P16" t="n">
-        <v>599.0397446017254</v>
+        <v>65.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>545.5261898799506</v>
+        <v>65.12</v>
       </c>
       <c r="R16" t="n">
         <v>65.12</v>
@@ -5509,19 +5509,19 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>456.4291130376557</v>
+        <v>887.4717564436343</v>
       </c>
       <c r="L17" t="n">
-        <v>456.4291130376557</v>
+        <v>1693.331756443634</v>
       </c>
       <c r="M17" t="n">
-        <v>967.2779417665907</v>
+        <v>2204.180585172569</v>
       </c>
       <c r="N17" t="n">
-        <v>1580.498261541354</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="O17" t="n">
-        <v>2386.358261541354</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P17" t="n">
         <v>2817.400904947332</v>
@@ -5585,19 +5585,19 @@
         <v>126.374877967565</v>
       </c>
       <c r="J18" t="n">
-        <v>250.3313981428639</v>
+        <v>404.4452825072959</v>
       </c>
       <c r="K18" t="n">
-        <v>439.5242142372473</v>
+        <v>593.6380986016793</v>
       </c>
       <c r="L18" t="n">
-        <v>864.9885601968793</v>
+        <v>864.9885601968795</v>
       </c>
       <c r="M18" t="n">
-        <v>951.0691019397386</v>
+        <v>1227.279101939739</v>
       </c>
       <c r="N18" t="n">
-        <v>1084.349386547307</v>
+        <v>1360.559386547307</v>
       </c>
       <c r="O18" t="n">
         <v>1599.601838231026</v>
@@ -5667,28 +5667,28 @@
         <v>859.3027230120967</v>
       </c>
       <c r="K19" t="n">
-        <v>859.3027230120967</v>
+        <v>849.6857797786189</v>
       </c>
       <c r="L19" t="n">
-        <v>859.3027230120967</v>
+        <v>849.6857797786189</v>
       </c>
       <c r="M19" t="n">
-        <v>859.3027230120967</v>
+        <v>605.6134450285685</v>
       </c>
       <c r="N19" t="n">
-        <v>859.3027230120967</v>
+        <v>605.6134450285685</v>
       </c>
       <c r="O19" t="n">
-        <v>859.3027230120967</v>
+        <v>605.6134450285685</v>
       </c>
       <c r="P19" t="n">
-        <v>859.3027230120967</v>
+        <v>605.6134450285685</v>
       </c>
       <c r="Q19" t="n">
-        <v>517.2433615971223</v>
+        <v>601.4589976606127</v>
       </c>
       <c r="R19" t="n">
-        <v>65.12</v>
+        <v>149.3356360634903</v>
       </c>
       <c r="S19" t="n">
         <v>65.12</v>
@@ -5746,22 +5746,22 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>1166.135479385524</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="L20" t="n">
-        <v>1693.331756443634</v>
+        <v>1262.289113037656</v>
       </c>
       <c r="M20" t="n">
-        <v>2204.180585172569</v>
+        <v>1773.137941766591</v>
       </c>
       <c r="N20" t="n">
-        <v>2817.400904947332</v>
+        <v>2386.358261541354</v>
       </c>
       <c r="O20" t="n">
-        <v>2817.400904947332</v>
+        <v>3192.218261541354</v>
       </c>
       <c r="P20" t="n">
-        <v>2817.400904947332</v>
+        <v>3192.218261541354</v>
       </c>
       <c r="Q20" t="n">
         <v>3256</v>
@@ -5822,22 +5822,22 @@
         <v>126.374877967565</v>
       </c>
       <c r="J21" t="n">
-        <v>404.4452825072959</v>
+        <v>250.3313981428639</v>
       </c>
       <c r="K21" t="n">
-        <v>593.6380986016793</v>
+        <v>715.7342142372473</v>
       </c>
       <c r="L21" t="n">
-        <v>864.9885601968793</v>
+        <v>987.0846758324474</v>
       </c>
       <c r="M21" t="n">
-        <v>951.0691019397386</v>
+        <v>1073.165217575307</v>
       </c>
       <c r="N21" t="n">
-        <v>1360.559386547307</v>
+        <v>1206.445502182875</v>
       </c>
       <c r="O21" t="n">
-        <v>1599.601838231026</v>
+        <v>1445.487953866594</v>
       </c>
       <c r="P21" t="n">
         <v>1712.131182700533</v>
@@ -5922,10 +5922,10 @@
         <v>859.3027230120967</v>
       </c>
       <c r="Q22" t="n">
-        <v>407.9499286428058</v>
+        <v>601.4589976606127</v>
       </c>
       <c r="R22" t="n">
-        <v>65.12</v>
+        <v>149.3356360634903</v>
       </c>
       <c r="S22" t="n">
         <v>65.12</v>
@@ -5956,13 +5956,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>879.6685602764463</v>
+        <v>880.1035184729978</v>
       </c>
       <c r="C23" t="n">
-        <v>707.4720165966545</v>
+        <v>707.906974793206</v>
       </c>
       <c r="D23" t="n">
-        <v>574.8062027180183</v>
+        <v>575.2411609145698</v>
       </c>
       <c r="E23" t="n">
         <v>448.6115754530863</v>
@@ -5980,19 +5980,19 @@
         <v>65.12</v>
       </c>
       <c r="J23" t="n">
-        <v>177.7653900957659</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="K23" t="n">
         <v>887.4717564436343</v>
       </c>
       <c r="L23" t="n">
-        <v>1693.331756443634</v>
+        <v>887.4717564436343</v>
       </c>
       <c r="M23" t="n">
-        <v>2204.180585172569</v>
+        <v>1398.320585172569</v>
       </c>
       <c r="N23" t="n">
-        <v>2817.400904947332</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="O23" t="n">
         <v>2817.400904947332</v>
@@ -6007,25 +6007,25 @@
         <v>3256</v>
       </c>
       <c r="S23" t="n">
-        <v>3037.971547674421</v>
+        <v>3038.406505870973</v>
       </c>
       <c r="T23" t="n">
-        <v>2727.188131786983</v>
+        <v>2727.623089983534</v>
       </c>
       <c r="U23" t="n">
-        <v>2353.227226182325</v>
+        <v>2353.662184378877</v>
       </c>
       <c r="V23" t="n">
-        <v>1998.832252276443</v>
+        <v>1999.267210472994</v>
       </c>
       <c r="W23" t="n">
-        <v>1635.828741184576</v>
+        <v>1636.263699381128</v>
       </c>
       <c r="X23" t="n">
-        <v>1319.382444759659</v>
+        <v>1319.817402956211</v>
       </c>
       <c r="Y23" t="n">
-        <v>1084.718371342683</v>
+        <v>1085.153329539235</v>
       </c>
     </row>
     <row r="24">
@@ -6065,16 +6065,16 @@
         <v>439.5242142372473</v>
       </c>
       <c r="L24" t="n">
-        <v>864.9885601968795</v>
+        <v>710.8746758324473</v>
       </c>
       <c r="M24" t="n">
-        <v>1227.279101939739</v>
+        <v>796.9552175753066</v>
       </c>
       <c r="N24" t="n">
-        <v>1360.559386547307</v>
+        <v>930.2355021828749</v>
       </c>
       <c r="O24" t="n">
-        <v>1599.601838231026</v>
+        <v>1323.391838231026</v>
       </c>
       <c r="P24" t="n">
         <v>1712.131182700533</v>
@@ -6156,10 +6156,10 @@
         <v>859.3027230120967</v>
       </c>
       <c r="P25" t="n">
-        <v>446.72908934717</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="Q25" t="n">
-        <v>65.12</v>
+        <v>407.9499286428058</v>
       </c>
       <c r="R25" t="n">
         <v>65.12</v>
@@ -6193,13 +6193,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>288.5819982252464</v>
+        <v>525.7388319673844</v>
       </c>
       <c r="C26" t="n">
-        <v>61.84</v>
+        <v>298.996833742138</v>
       </c>
       <c r="D26" t="n">
-        <v>61.84</v>
+        <v>111.7855653180473</v>
       </c>
       <c r="E26" t="n">
         <v>61.84</v>
@@ -6220,19 +6220,19 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K26" t="n">
-        <v>1162.855479385524</v>
+        <v>764.0617564436071</v>
       </c>
       <c r="L26" t="n">
-        <v>1928.125479385524</v>
+        <v>764.0617564436071</v>
       </c>
       <c r="M26" t="n">
-        <v>2438.974308114459</v>
+        <v>1274.910585172542</v>
       </c>
       <c r="N26" t="n">
-        <v>2653.400904947332</v>
+        <v>1888.130904947305</v>
       </c>
       <c r="O26" t="n">
-        <v>2653.400904947332</v>
+        <v>1888.130904947305</v>
       </c>
       <c r="P26" t="n">
         <v>2653.400904947332</v>
@@ -6244,25 +6244,25 @@
         <v>3065.860001183541</v>
       </c>
       <c r="S26" t="n">
-        <v>2793.286094312508</v>
+        <v>3065.860001183541</v>
       </c>
       <c r="T26" t="n">
-        <v>2427.957223879615</v>
+        <v>2700.531130750648</v>
       </c>
       <c r="U26" t="n">
-        <v>1999.450863729503</v>
+        <v>2272.024770600536</v>
       </c>
       <c r="V26" t="n">
-        <v>1590.510435278166</v>
+        <v>1863.084342149199</v>
       </c>
       <c r="W26" t="n">
-        <v>1172.961469640845</v>
+        <v>1445.535376511878</v>
       </c>
       <c r="X26" t="n">
-        <v>801.9697186704736</v>
+        <v>1074.543625541507</v>
       </c>
       <c r="Y26" t="n">
-        <v>512.760190708043</v>
+        <v>785.3340975790759</v>
       </c>
     </row>
     <row r="27">
@@ -6296,10 +6296,10 @@
         <v>69.63487796756496</v>
       </c>
       <c r="J27" t="n">
-        <v>212.5171006891147</v>
+        <v>416.3413981428639</v>
       </c>
       <c r="K27" t="n">
-        <v>624.4599167834981</v>
+        <v>828.2842142372474</v>
       </c>
       <c r="L27" t="n">
         <v>1118.560378378698</v>
@@ -6378,28 +6378,28 @@
         <v>406.0589893823512</v>
       </c>
       <c r="K28" t="n">
-        <v>341.8965916034189</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="L28" t="n">
-        <v>341.8965916034189</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="M28" t="n">
-        <v>200.6010906089449</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="N28" t="n">
-        <v>200.6010906089449</v>
+        <v>61.84</v>
       </c>
       <c r="O28" t="n">
-        <v>200.6010906089449</v>
+        <v>61.84</v>
       </c>
       <c r="P28" t="n">
-        <v>200.6010906089449</v>
+        <v>61.84</v>
       </c>
       <c r="Q28" t="n">
-        <v>200.6010906089449</v>
+        <v>61.84</v>
       </c>
       <c r="R28" t="n">
-        <v>200.6010906089449</v>
+        <v>61.84</v>
       </c>
       <c r="S28" t="n">
         <v>61.84</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>475.7932666493371</v>
+        <v>785.3340975790759</v>
       </c>
       <c r="C29" t="n">
-        <v>249.0512684240907</v>
+        <v>785.3340975790759</v>
       </c>
       <c r="D29" t="n">
-        <v>61.84</v>
+        <v>785.3340975790759</v>
       </c>
       <c r="E29" t="n">
-        <v>61.84</v>
+        <v>608.9679390894501</v>
       </c>
       <c r="F29" t="n">
-        <v>61.84</v>
+        <v>427.2612434247916</v>
       </c>
       <c r="G29" t="n">
-        <v>61.84</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="H29" t="n">
         <v>61.84</v>
@@ -6454,19 +6454,19 @@
         <v>61.84</v>
       </c>
       <c r="J29" t="n">
-        <v>61.84</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="K29" t="n">
-        <v>771.5463663478683</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="L29" t="n">
-        <v>1536.816366347868</v>
+        <v>764.0617564435998</v>
       </c>
       <c r="M29" t="n">
-        <v>2040.180585172569</v>
+        <v>1274.910585172535</v>
       </c>
       <c r="N29" t="n">
-        <v>2653.400904947332</v>
+        <v>1888.130904947298</v>
       </c>
       <c r="O29" t="n">
         <v>2653.400904947332</v>
@@ -6478,28 +6478,28 @@
         <v>3092</v>
       </c>
       <c r="R29" t="n">
-        <v>3092</v>
+        <v>3065.860001183541</v>
       </c>
       <c r="S29" t="n">
-        <v>3015.914435865494</v>
+        <v>3065.860001183541</v>
       </c>
       <c r="T29" t="n">
-        <v>2650.585565432601</v>
+        <v>2700.531130750648</v>
       </c>
       <c r="U29" t="n">
-        <v>2222.079205282489</v>
+        <v>2272.024770600536</v>
       </c>
       <c r="V29" t="n">
-        <v>1813.138776831152</v>
+        <v>1863.084342149199</v>
       </c>
       <c r="W29" t="n">
-        <v>1395.589811193831</v>
+        <v>1445.535376511878</v>
       </c>
       <c r="X29" t="n">
-        <v>1024.598060223459</v>
+        <v>1074.543625541507</v>
       </c>
       <c r="Y29" t="n">
-        <v>735.3885322610286</v>
+        <v>785.3340975790759</v>
       </c>
     </row>
     <row r="30">
@@ -6530,7 +6530,7 @@
         <v>61.84</v>
       </c>
       <c r="I30" t="n">
-        <v>69.63487796756496</v>
+        <v>61.84</v>
       </c>
       <c r="J30" t="n">
         <v>212.5171006891147</v>
@@ -6633,7 +6633,7 @@
         <v>406.0589893823512</v>
       </c>
       <c r="Q31" t="n">
-        <v>406.0589893823512</v>
+        <v>61.84</v>
       </c>
       <c r="R31" t="n">
         <v>61.84</v>
@@ -6691,52 +6691,52 @@
         <v>61.84</v>
       </c>
       <c r="J32" t="n">
-        <v>445.5561922637026</v>
+        <v>445.5561922637025</v>
       </c>
       <c r="K32" t="n">
-        <v>1155.05686870288</v>
+        <v>1155.056868702875</v>
       </c>
       <c r="L32" t="n">
-        <v>1139.518787894799</v>
+        <v>1920.326868702875</v>
       </c>
       <c r="M32" t="n">
-        <v>1645.201836286733</v>
+        <v>2426.009917094809</v>
       </c>
       <c r="N32" t="n">
-        <v>1629.663755478651</v>
+        <v>3036.143012467487</v>
       </c>
       <c r="O32" t="n">
-        <v>1894.763647533204</v>
+        <v>3092</v>
       </c>
       <c r="P32" t="n">
-        <v>2660.033647533245</v>
+        <v>3076.461919191918</v>
       </c>
       <c r="Q32" t="n">
         <v>3092</v>
       </c>
       <c r="R32" t="n">
-        <v>3083.457988499581</v>
+        <v>3092</v>
       </c>
       <c r="S32" t="n">
-        <v>2877.550748295214</v>
+        <v>2886.092759795633</v>
       </c>
       <c r="T32" t="n">
-        <v>2578.888544528988</v>
+        <v>2587.430556029407</v>
       </c>
       <c r="U32" t="n">
-        <v>2217.048851045543</v>
+        <v>2225.590862545962</v>
       </c>
       <c r="V32" t="n">
-        <v>1874.775089260873</v>
+        <v>1883.317100761291</v>
       </c>
       <c r="W32" t="n">
-        <v>1523.892790290219</v>
+        <v>1532.434801790637</v>
       </c>
       <c r="X32" t="n">
-        <v>1219.567705986514</v>
+        <v>1228.109717486932</v>
       </c>
       <c r="Y32" t="n">
-        <v>997.0248446907499</v>
+        <v>1005.566856191168</v>
       </c>
     </row>
     <row r="33">
@@ -6773,22 +6773,22 @@
         <v>185.796520175299</v>
       </c>
       <c r="K33" t="n">
-        <v>501.5214443439232</v>
+        <v>374.9893362696823</v>
       </c>
       <c r="L33" t="n">
-        <v>1060.961905939123</v>
+        <v>646.3397978648825</v>
       </c>
       <c r="M33" t="n">
-        <v>1147.042447681983</v>
+        <v>732.4203396077418</v>
       </c>
       <c r="N33" t="n">
-        <v>1280.322732289551</v>
+        <v>875.4912047291255</v>
       </c>
       <c r="O33" t="n">
-        <v>1519.36518397327</v>
+        <v>1402.623656412844</v>
       </c>
       <c r="P33" t="n">
-        <v>1631.894528442776</v>
+        <v>1515.153000882351</v>
       </c>
       <c r="Q33" t="n">
         <v>1631.894528442776</v>
@@ -6825,46 +6825,46 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>486.0066123122328</v>
+        <v>486.0066123122566</v>
       </c>
       <c r="C34" t="n">
-        <v>504.0986181306686</v>
+        <v>504.0986181306923</v>
       </c>
       <c r="D34" t="n">
-        <v>509.5077622556687</v>
+        <v>509.5077622556924</v>
       </c>
       <c r="E34" t="n">
-        <v>519.4266664670818</v>
+        <v>519.4266664671054</v>
       </c>
       <c r="F34" t="n">
-        <v>535.8776390590173</v>
+        <v>535.8776390590409</v>
       </c>
       <c r="G34" t="n">
-        <v>581.3742049459025</v>
+        <v>581.3742049459262</v>
       </c>
       <c r="H34" t="n">
-        <v>642.9807901053001</v>
+        <v>642.9807901053238</v>
       </c>
       <c r="I34" t="n">
-        <v>756.203669041383</v>
+        <v>756.2036690414067</v>
       </c>
       <c r="J34" t="n">
-        <v>1009.377409693834</v>
+        <v>1009.377409693858</v>
       </c>
       <c r="K34" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="L34" t="n">
-        <v>929.781667427525</v>
+        <v>877.9453505420606</v>
       </c>
       <c r="M34" t="n">
-        <v>697.8305447986868</v>
+        <v>815.2677387952449</v>
       </c>
       <c r="N34" t="n">
-        <v>414.8153172515302</v>
+        <v>815.2677387952449</v>
       </c>
       <c r="O34" t="n">
-        <v>61.84</v>
+        <v>462.2924215437147</v>
       </c>
       <c r="P34" t="n">
         <v>61.84</v>
@@ -6904,25 +6904,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C35" t="n">
-        <v>652.5629256875638</v>
+        <v>644.0209141871454</v>
       </c>
       <c r="D35" t="n">
-        <v>532.0183239301398</v>
+        <v>523.4763124297214</v>
       </c>
       <c r="E35" t="n">
-        <v>417.5099505898684</v>
+        <v>408.96793908945</v>
       </c>
       <c r="F35" t="n">
-        <v>302.4699215918766</v>
+        <v>293.9279100914582</v>
       </c>
       <c r="G35" t="n">
-        <v>188.5735859484259</v>
+        <v>180.0315744480075</v>
       </c>
       <c r="H35" t="n">
-        <v>70.38201150041843</v>
+        <v>61.84</v>
       </c>
       <c r="I35" t="n">
         <v>61.84</v>
@@ -6931,19 +6931,19 @@
         <v>445.5561922637025</v>
       </c>
       <c r="K35" t="n">
-        <v>1155.056868702876</v>
+        <v>1154.134391781985</v>
       </c>
       <c r="L35" t="n">
-        <v>1920.326868702876</v>
+        <v>1139.5187878948</v>
       </c>
       <c r="M35" t="n">
-        <v>1904.788787894794</v>
+        <v>1123.980707086718</v>
       </c>
       <c r="N35" t="n">
-        <v>1889.250707086712</v>
+        <v>1129.493647533147</v>
       </c>
       <c r="O35" t="n">
-        <v>1894.763647533197</v>
+        <v>1894.763647533196</v>
       </c>
       <c r="P35" t="n">
         <v>2660.033647533245</v>
@@ -6973,7 +6973,7 @@
         <v>1228.109717486932</v>
       </c>
       <c r="Y35" t="n">
-        <v>1005.566856191168</v>
+        <v>997.0248446907499</v>
       </c>
     </row>
     <row r="36">
@@ -7004,22 +7004,22 @@
         <v>61.84</v>
       </c>
       <c r="I36" t="n">
-        <v>134.974877967565</v>
+        <v>61.84</v>
       </c>
       <c r="J36" t="n">
-        <v>258.9313981428639</v>
+        <v>185.796520175299</v>
       </c>
       <c r="K36" t="n">
-        <v>448.1242142372473</v>
+        <v>374.9893362696823</v>
       </c>
       <c r="L36" t="n">
-        <v>719.4746758324475</v>
+        <v>646.3397978648825</v>
       </c>
       <c r="M36" t="n">
-        <v>1030.300920121557</v>
+        <v>1020.510339607742</v>
       </c>
       <c r="N36" t="n">
-        <v>1163.581204729126</v>
+        <v>1153.79062421531</v>
       </c>
       <c r="O36" t="n">
         <v>1402.623656412844</v>
@@ -7062,46 +7062,46 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>486.0066123122566</v>
+        <v>486.0066123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>504.0986181306923</v>
+        <v>504.0986181306686</v>
       </c>
       <c r="D37" t="n">
-        <v>509.5077622556924</v>
+        <v>509.5077622556687</v>
       </c>
       <c r="E37" t="n">
-        <v>519.4266664671054</v>
+        <v>519.4266664670818</v>
       </c>
       <c r="F37" t="n">
-        <v>535.8776390590409</v>
+        <v>535.8776390590173</v>
       </c>
       <c r="G37" t="n">
-        <v>581.3742049459262</v>
+        <v>581.3742049459025</v>
       </c>
       <c r="H37" t="n">
-        <v>642.9807901053238</v>
+        <v>642.9807901053001</v>
       </c>
       <c r="I37" t="n">
-        <v>756.2036690414067</v>
+        <v>756.203669041383</v>
       </c>
       <c r="J37" t="n">
-        <v>1009.377409693858</v>
+        <v>1009.377409693834</v>
       </c>
       <c r="K37" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="L37" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="M37" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="N37" t="n">
-        <v>1011.831843630726</v>
+        <v>941.0737317239891</v>
       </c>
       <c r="O37" t="n">
-        <v>1011.831843630726</v>
+        <v>941.0737317239891</v>
       </c>
       <c r="P37" t="n">
         <v>941.0737317239891</v>
@@ -7168,19 +7168,19 @@
         <v>61.84</v>
       </c>
       <c r="K38" t="n">
-        <v>771.3406764391794</v>
+        <v>771.3406764391735</v>
       </c>
       <c r="L38" t="n">
-        <v>1536.610676439179</v>
+        <v>755.8025956310926</v>
       </c>
       <c r="M38" t="n">
-        <v>1576.998080807972</v>
+        <v>1261.485644023026</v>
       </c>
       <c r="N38" t="n">
-        <v>1561.45999999989</v>
+        <v>1561.459999999888</v>
       </c>
       <c r="O38" t="n">
-        <v>2326.729999999945</v>
+        <v>2326.729999999944</v>
       </c>
       <c r="P38" t="n">
         <v>3092</v>
@@ -7189,25 +7189,25 @@
         <v>3092</v>
       </c>
       <c r="R38" t="n">
-        <v>3092</v>
+        <v>3083.457988499581</v>
       </c>
       <c r="S38" t="n">
-        <v>2886.092759795633</v>
+        <v>2877.550748295214</v>
       </c>
       <c r="T38" t="n">
-        <v>2587.430556029407</v>
+        <v>2578.888544528988</v>
       </c>
       <c r="U38" t="n">
-        <v>2225.590862545962</v>
+        <v>2217.048851045543</v>
       </c>
       <c r="V38" t="n">
-        <v>1883.317100761291</v>
+        <v>1874.775089260873</v>
       </c>
       <c r="W38" t="n">
-        <v>1532.434801790637</v>
+        <v>1523.892790290219</v>
       </c>
       <c r="X38" t="n">
-        <v>1228.109717486932</v>
+        <v>1219.567705986514</v>
       </c>
       <c r="Y38" t="n">
         <v>997.0248446907499</v>
@@ -7244,25 +7244,25 @@
         <v>134.974877967565</v>
       </c>
       <c r="J39" t="n">
-        <v>258.9313981428639</v>
+        <v>547.0213981428639</v>
       </c>
       <c r="K39" t="n">
-        <v>448.1242142372473</v>
+        <v>736.2142142372472</v>
       </c>
       <c r="L39" t="n">
-        <v>719.4746758324475</v>
+        <v>1007.564675832447</v>
       </c>
       <c r="M39" t="n">
-        <v>805.5552175753068</v>
+        <v>1093.645217575307</v>
       </c>
       <c r="N39" t="n">
-        <v>938.8355021828751</v>
+        <v>1226.925502182875</v>
       </c>
       <c r="O39" t="n">
-        <v>1402.623656412844</v>
+        <v>1465.967953866594</v>
       </c>
       <c r="P39" t="n">
-        <v>1515.153000882351</v>
+        <v>1578.4972983361</v>
       </c>
       <c r="Q39" t="n">
         <v>1631.894528442776</v>
@@ -7299,49 +7299,49 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>486.0066123122328</v>
+        <v>486.0066123122601</v>
       </c>
       <c r="C40" t="n">
-        <v>504.0986181306686</v>
+        <v>504.0986181306959</v>
       </c>
       <c r="D40" t="n">
-        <v>509.5077622556687</v>
+        <v>509.507762255696</v>
       </c>
       <c r="E40" t="n">
-        <v>519.4266664670818</v>
+        <v>519.426666467109</v>
       </c>
       <c r="F40" t="n">
-        <v>535.8776390590173</v>
+        <v>535.8776390590446</v>
       </c>
       <c r="G40" t="n">
-        <v>581.3742049459025</v>
+        <v>581.3742049459298</v>
       </c>
       <c r="H40" t="n">
-        <v>642.9807901053001</v>
+        <v>642.9807901053274</v>
       </c>
       <c r="I40" t="n">
-        <v>756.203669041383</v>
+        <v>756.2036690414103</v>
       </c>
       <c r="J40" t="n">
-        <v>1009.377409693834</v>
+        <v>1009.377409693862</v>
       </c>
       <c r="K40" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.83184363073</v>
       </c>
       <c r="L40" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.83184363073</v>
       </c>
       <c r="M40" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.83184363073</v>
       </c>
       <c r="N40" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.83184363073</v>
       </c>
       <c r="O40" t="n">
-        <v>1011.831843630703</v>
+        <v>902.2945710196249</v>
       </c>
       <c r="P40" t="n">
-        <v>941.0737317239891</v>
+        <v>501.8421494759102</v>
       </c>
       <c r="Q40" t="n">
         <v>501.8421494759102</v>
@@ -7378,16 +7378,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>845.2760936952099</v>
+        <v>697.0151441276475</v>
       </c>
       <c r="C41" t="n">
-        <v>845.2760936952099</v>
+        <v>458.1519337811891</v>
       </c>
       <c r="D41" t="n">
-        <v>645.943613149907</v>
+        <v>258.8194532358863</v>
       </c>
       <c r="E41" t="n">
-        <v>452.6473610217569</v>
+        <v>258.8194532358863</v>
       </c>
       <c r="F41" t="n">
         <v>258.8194532358863</v>
@@ -7402,22 +7402,22 @@
         <v>61.84</v>
       </c>
       <c r="J41" t="n">
-        <v>61.84</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="K41" t="n">
-        <v>61.84</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="L41" t="n">
-        <v>61.84</v>
+        <v>764.0617564435712</v>
       </c>
       <c r="M41" t="n">
-        <v>572.6888287289351</v>
+        <v>1274.910585172506</v>
       </c>
       <c r="N41" t="n">
-        <v>1185.909148503698</v>
+        <v>1888.130904947269</v>
       </c>
       <c r="O41" t="n">
-        <v>1888.13090494727</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="P41" t="n">
         <v>2653.400904947332</v>
@@ -7438,16 +7438,16 @@
         <v>1950.966015244655</v>
       </c>
       <c r="V41" t="n">
-        <v>1801.43627460334</v>
+        <v>1529.904374672105</v>
       </c>
       <c r="W41" t="n">
-        <v>1801.43627460334</v>
+        <v>1100.234196913573</v>
       </c>
       <c r="X41" t="n">
-        <v>1418.323311511756</v>
+        <v>968.7316218605511</v>
       </c>
       <c r="Y41" t="n">
-        <v>1116.992571428113</v>
+        <v>968.7316218605511</v>
       </c>
     </row>
     <row r="42">
@@ -7493,31 +7493,31 @@
         <v>1575.900339607742</v>
       </c>
       <c r="N42" t="n">
-        <v>1920.05062421531</v>
+        <v>1718.696291488086</v>
       </c>
       <c r="O42" t="n">
-        <v>2369.963075899029</v>
+        <v>2168.608743171805</v>
       </c>
       <c r="P42" t="n">
-        <v>2639.504256588441</v>
+        <v>2492.008087641312</v>
       </c>
       <c r="Q42" t="n">
-        <v>2679.025784148866</v>
+        <v>2531.529615201737</v>
       </c>
       <c r="R42" t="n">
-        <v>2341.375483853533</v>
+        <v>2480.230476522543</v>
       </c>
       <c r="S42" t="n">
-        <v>2085.250231364027</v>
+        <v>2224.105224033037</v>
       </c>
       <c r="T42" t="n">
-        <v>1890.949458417043</v>
+        <v>2029.804451086053</v>
       </c>
       <c r="U42" t="n">
-        <v>1701.848084921905</v>
+        <v>1840.703077590915</v>
       </c>
       <c r="V42" t="n">
-        <v>1498.301956445622</v>
+        <v>1637.156949114632</v>
       </c>
       <c r="W42" t="n">
         <v>1415.567915872381</v>
@@ -7536,40 +7536,40 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>77.77043040567538</v>
+        <v>126.3903759570681</v>
       </c>
       <c r="C43" t="n">
-        <v>77.77043040567538</v>
+        <v>126.3903759570681</v>
       </c>
       <c r="D43" t="n">
-        <v>77.77043040567538</v>
+        <v>126.3903759570681</v>
       </c>
       <c r="E43" t="n">
-        <v>77.77043040567538</v>
+        <v>126.3903759570681</v>
       </c>
       <c r="F43" t="n">
-        <v>77.77043040567538</v>
+        <v>126.3903759570681</v>
       </c>
       <c r="G43" t="n">
-        <v>77.77043040567538</v>
+        <v>126.3903759570681</v>
       </c>
       <c r="H43" t="n">
-        <v>61.84</v>
+        <v>110.4599455513927</v>
       </c>
       <c r="I43" t="n">
-        <v>61.84</v>
+        <v>146.4628244874756</v>
       </c>
       <c r="J43" t="n">
-        <v>61.84</v>
+        <v>322.4165651399269</v>
       </c>
       <c r="K43" t="n">
-        <v>61.84</v>
+        <v>322.4165651399269</v>
       </c>
       <c r="L43" t="n">
-        <v>61.84</v>
+        <v>322.4165651399269</v>
       </c>
       <c r="M43" t="n">
-        <v>61.84</v>
+        <v>322.4165651399269</v>
       </c>
       <c r="N43" t="n">
         <v>61.84</v>
@@ -7590,22 +7590,22 @@
         <v>61.84</v>
       </c>
       <c r="T43" t="n">
-        <v>61.84</v>
+        <v>64.78567915880487</v>
       </c>
       <c r="U43" t="n">
-        <v>77.58692624569879</v>
+        <v>126.2068717970915</v>
       </c>
       <c r="V43" t="n">
-        <v>91.27831913164476</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="W43" t="n">
-        <v>77.77043040567538</v>
+        <v>126.3903759570681</v>
       </c>
       <c r="X43" t="n">
-        <v>77.77043040567538</v>
+        <v>126.3903759570681</v>
       </c>
       <c r="Y43" t="n">
-        <v>77.77043040567538</v>
+        <v>126.3903759570681</v>
       </c>
     </row>
     <row r="44">
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>510.6771863064416</v>
+        <v>439.1244153760538</v>
       </c>
       <c r="C44" t="n">
-        <v>510.6771863064416</v>
+        <v>173.998578766969</v>
       </c>
       <c r="D44" t="n">
-        <v>285.0820794985125</v>
+        <v>173.998578766969</v>
       </c>
       <c r="E44" t="n">
-        <v>285.0820794985125</v>
+        <v>173.998578766969</v>
       </c>
       <c r="F44" t="n">
-        <v>285.0820794985125</v>
+        <v>173.998578766969</v>
       </c>
       <c r="G44" t="n">
-        <v>285.0820794985125</v>
+        <v>61.84</v>
       </c>
       <c r="H44" t="n">
         <v>61.84</v>
@@ -7639,25 +7639,25 @@
         <v>61.84</v>
       </c>
       <c r="J44" t="n">
-        <v>61.84</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="K44" t="n">
-        <v>771.5463663478683</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="L44" t="n">
-        <v>1536.816366347868</v>
+        <v>1928.125479385524</v>
       </c>
       <c r="M44" t="n">
-        <v>2047.665195076803</v>
+        <v>1928.125479385524</v>
       </c>
       <c r="N44" t="n">
-        <v>2660.885514851566</v>
+        <v>2541.345799160287</v>
       </c>
       <c r="O44" t="n">
-        <v>3092</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="P44" t="n">
-        <v>3092</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="Q44" t="n">
         <v>3092</v>
@@ -7666,25 +7666,25 @@
         <v>3092</v>
       </c>
       <c r="S44" t="n">
-        <v>3092</v>
+        <v>2781.042254745129</v>
       </c>
       <c r="T44" t="n">
-        <v>2688.287291183269</v>
+        <v>2377.329545928397</v>
       </c>
       <c r="U44" t="n">
-        <v>2221.397092649318</v>
+        <v>2377.329545928397</v>
       </c>
       <c r="V44" t="n">
-        <v>1774.072825814143</v>
+        <v>1930.005279093222</v>
       </c>
       <c r="W44" t="n">
-        <v>1318.140021792984</v>
+        <v>1474.072475072062</v>
       </c>
       <c r="X44" t="n">
-        <v>908.7644324387737</v>
+        <v>1064.696885717853</v>
       </c>
       <c r="Y44" t="n">
-        <v>581.1710660925046</v>
+        <v>737.1035193715836</v>
       </c>
     </row>
     <row r="45">
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>864.2804224150209</v>
+        <v>1028.890452379605</v>
       </c>
       <c r="C45" t="n">
         <v>853.031954959888</v>
@@ -7721,49 +7721,49 @@
         <v>370.9265201752989</v>
       </c>
       <c r="K45" t="n">
-        <v>659.2388776463674</v>
+        <v>625.3344931834415</v>
       </c>
       <c r="L45" t="n">
-        <v>1115.719339241567</v>
+        <v>1081.814954778642</v>
       </c>
       <c r="M45" t="n">
-        <v>1386.929880984427</v>
+        <v>1353.025496521501</v>
       </c>
       <c r="N45" t="n">
-        <v>1705.340165591995</v>
+        <v>1671.435781129069</v>
       </c>
       <c r="O45" t="n">
-        <v>2129.512617275714</v>
+        <v>2095.608232812788</v>
       </c>
       <c r="P45" t="n">
-        <v>2427.171961745221</v>
+        <v>2393.267577282295</v>
       </c>
       <c r="Q45" t="n">
-        <v>2427.171961745221</v>
+        <v>2407.04910484272</v>
       </c>
       <c r="R45" t="n">
-        <v>2427.171961745221</v>
+        <v>2407.04910484272</v>
       </c>
       <c r="S45" t="n">
-        <v>2427.171961745221</v>
+        <v>2343.930332204927</v>
       </c>
       <c r="T45" t="n">
-        <v>2206.608562535611</v>
+        <v>2123.366932995317</v>
       </c>
       <c r="U45" t="n">
-        <v>1991.244562777847</v>
+        <v>1908.002933237553</v>
       </c>
       <c r="V45" t="n">
-        <v>1761.435808038937</v>
+        <v>1678.194178498644</v>
       </c>
       <c r="W45" t="n">
-        <v>1513.58414853406</v>
+        <v>1678.194178498644</v>
       </c>
       <c r="X45" t="n">
-        <v>1278.369260205386</v>
+        <v>1442.979290169969</v>
       </c>
       <c r="Y45" t="n">
-        <v>1063.832499835553</v>
+        <v>1228.442529800137</v>
       </c>
     </row>
     <row r="46">
@@ -7797,40 +7797,40 @@
         <v>61.84</v>
       </c>
       <c r="J46" t="n">
-        <v>61.84</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="K46" t="n">
-        <v>61.84</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="L46" t="n">
-        <v>61.84</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="M46" t="n">
-        <v>61.84</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="N46" t="n">
-        <v>61.84</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="O46" t="n">
-        <v>61.84</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="P46" t="n">
-        <v>61.84</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="Q46" t="n">
-        <v>61.84</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="R46" t="n">
-        <v>61.84</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="S46" t="n">
-        <v>61.84</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="T46" t="n">
-        <v>61.84</v>
+        <v>74.13324264264263</v>
       </c>
       <c r="U46" t="n">
-        <v>61.84</v>
+        <v>74.13324264264263</v>
       </c>
       <c r="V46" t="n">
         <v>61.84</v>
@@ -7964,25 +7964,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>430.3047365861567</v>
+        <v>51.24160624509022</v>
       </c>
       <c r="K2" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>782.4479756267968</v>
       </c>
       <c r="M2" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N2" t="n">
-        <v>582.6427212635809</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O2" t="n">
         <v>884.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814674</v>
       </c>
       <c r="Q2" t="n">
         <v>615.8520732695737</v>
@@ -8201,25 +8201,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>430.3047365861567</v>
+        <v>51.24160624509022</v>
       </c>
       <c r="K5" t="n">
-        <v>306.2599628088302</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M5" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N5" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O5" t="n">
-        <v>884.2478695740924</v>
+        <v>233.2813807819365</v>
       </c>
       <c r="P5" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814674</v>
       </c>
       <c r="Q5" t="n">
         <v>615.8520732695737</v>
@@ -8441,7 +8441,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>500.8454983898731</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -8459,7 +8459,7 @@
         <v>0.2870600406860149</v>
       </c>
       <c r="Q8" t="n">
-        <v>615.8520732695737</v>
+        <v>399.8224541363476</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,7 +8678,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230994</v>
+        <v>240.811073919941</v>
       </c>
       <c r="L11" t="n">
         <v>814</v>
@@ -8687,16 +8687,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O11" t="n">
-        <v>231.79875049407</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,7 +8912,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>148.8262285640457</v>
       </c>
       <c r="K14" t="n">
         <v>716.8751175230994</v>
@@ -8933,7 +8933,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
-        <v>334.3735652474629</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,10 +9152,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>435.3966095009885</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
@@ -9164,10 +9164,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>884.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P17" t="n">
-        <v>435.68366954167</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
         <v>615.8520732695737</v>
@@ -9389,10 +9389,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>532.5214919778891</v>
+        <v>814</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
@@ -9401,13 +9401,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>70.24786957409245</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P20" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>237.2486827705622</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,13 +9623,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>148.8262285640457</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>435.3966095009885</v>
       </c>
       <c r="L23" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
@@ -9638,7 +9638,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>70.24786957409245</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P23" t="n">
         <v>0.2870600406814136</v>
@@ -9863,22 +9863,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>314.0531751575267</v>
       </c>
       <c r="L26" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>693.8414801232425</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.287060040709</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10097,22 +10097,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>772.9999999999999</v>
+        <v>314.0531751575193</v>
       </c>
       <c r="M29" t="n">
-        <v>1052.710833525854</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>70.24786957409245</v>
+        <v>843.2478695741272</v>
       </c>
       <c r="P29" t="n">
         <v>0.2870600406814136</v>
@@ -10340,22 +10340,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>773.0000000000002</v>
       </c>
       <c r="M32" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>348.0794627081009</v>
+        <v>140.928987231281</v>
       </c>
       <c r="P32" t="n">
-        <v>773.2870600407226</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>203.5880843274874</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10577,19 +10577,19 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L35" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>544.2621276423173</v>
       </c>
       <c r="N35" t="n">
-        <v>477.2489580698352</v>
+        <v>498.0894691118013</v>
       </c>
       <c r="O35" t="n">
-        <v>91.0883806161138</v>
+        <v>843.2478695741418</v>
       </c>
       <c r="P35" t="n">
-        <v>773.2870600407299</v>
+        <v>773.2870600407308</v>
       </c>
       <c r="Q35" t="n">
         <v>615.8520732695737</v>
@@ -10814,19 +10814,19 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L38" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>599.6283579674232</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>477.2489580698352</v>
+        <v>789.6062704869298</v>
       </c>
       <c r="O38" t="n">
-        <v>843.2478695741481</v>
+        <v>843.247869574149</v>
       </c>
       <c r="P38" t="n">
-        <v>773.2870600407372</v>
+        <v>773.2870600407381</v>
       </c>
       <c r="Q38" t="n">
         <v>188.2053843274866</v>
@@ -11045,13 +11045,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>314.0531751574904</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
@@ -11060,10 +11060,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O41" t="n">
-        <v>779.5627750726499</v>
+        <v>843.2478695741563</v>
       </c>
       <c r="P41" t="n">
-        <v>773.2870600407444</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11282,28 +11282,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>772.9999999999999</v>
+        <v>773</v>
       </c>
       <c r="M44" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N44" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O44" t="n">
-        <v>505.7170464917023</v>
+        <v>183.4348451165624</v>
       </c>
       <c r="P44" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22700,10 +22700,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.662449696447283</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>29.21007785422461</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22940,7 +22940,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>5.662449696459205</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>5.662449696442934</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23174,10 +23174,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.662449696442778</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>29.21007785422688</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23232,16 +23232,16 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>179.3632896068686</v>
+        <v>128.709941299406</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23271,10 +23271,10 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>35.41065930916164</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -23289,10 +23289,10 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>367.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -23423,10 +23423,10 @@
         <v>415.445564079015</v>
       </c>
       <c r="P13" t="n">
-        <v>462.4478973282775</v>
+        <v>121.6710978397498</v>
       </c>
       <c r="Q13" t="n">
-        <v>160.0624669370703</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
         <v>501.6021279811511</v>
@@ -23469,16 +23469,16 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>86.30994672070055</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H14" t="n">
-        <v>157.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23511,7 +23511,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>235.4209499110585</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -23657,16 +23657,16 @@
         <v>320.1850752716849</v>
       </c>
       <c r="O16" t="n">
-        <v>389.445564079015</v>
+        <v>297.3129142515843</v>
       </c>
       <c r="P16" t="n">
-        <v>436.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>421.860847251041</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S16" t="n">
         <v>111.3734797028554</v>
@@ -23882,13 +23882,13 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>9.520773801143037</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>144.5476281577792</v>
       </c>
       <c r="M19" t="n">
-        <v>241.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>292.1850752716849</v>
@@ -23900,13 +23900,13 @@
         <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>108.2004986247733</v>
+        <v>442.7263635313217</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24137,13 +24137,13 @@
         <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>191.5739783276288</v>
       </c>
       <c r="R22" t="n">
-        <v>108.2004986247733</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24180,7 +24180,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4306086145860064</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.430608614585708</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24371,13 +24371,13 @@
         <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>69.04626797189974</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>447.6021279811511</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="S25" t="n">
         <v>83.37347970285543</v>
@@ -24408,16 +24408,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>35.06290239760588</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>179.3632896068686</v>
+        <v>129.9171799420018</v>
       </c>
       <c r="F26" t="n">
         <v>179.8896287080119</v>
@@ -24459,7 +24459,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -24593,16 +24593,16 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>63.52077380114304</v>
       </c>
       <c r="L28" t="n">
         <v>198.5476281577792</v>
       </c>
       <c r="M28" t="n">
-        <v>155.7490654180206</v>
+        <v>295.6316114025499</v>
       </c>
       <c r="N28" t="n">
-        <v>346.1850752716849</v>
+        <v>5.408275783157251</v>
       </c>
       <c r="O28" t="n">
         <v>415.445564079015</v>
@@ -24617,7 +24617,7 @@
         <v>501.6021279811511</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24645,25 +24645,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>179.3632896068686</v>
+        <v>4.760792702139071</v>
       </c>
       <c r="F29" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24693,10 +24693,10 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>194.5234593091619</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -24848,10 +24848,10 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q31" t="n">
-        <v>500.839266425598</v>
+        <v>160.0624669370703</v>
       </c>
       <c r="R31" t="n">
-        <v>160.8253284926234</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S31" t="n">
         <v>137.3734797028554</v>
@@ -25070,19 +25070,19 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>51.31795371663317</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>167.5807757732023</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>396.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>434.839266425598</v>
@@ -25313,13 +25313,13 @@
         <v>229.6316114025499</v>
       </c>
       <c r="N37" t="n">
-        <v>280.1850752716849</v>
+        <v>210.1345444840384</v>
       </c>
       <c r="O37" t="n">
         <v>349.445564079015</v>
       </c>
       <c r="P37" t="n">
-        <v>326.3973665406075</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -25553,13 +25553,13 @@
         <v>280.1850752716849</v>
       </c>
       <c r="O40" t="n">
-        <v>349.445564079015</v>
+        <v>241.0036641940208</v>
       </c>
       <c r="P40" t="n">
-        <v>326.3973665406309</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -25596,16 +25596,16 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>236.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>191.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>191.8896287080119</v>
       </c>
       <c r="G41" t="n">
         <v>190.7573722870162</v>
@@ -25653,16 +25653,16 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>268.8165809319221</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>425.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>249.0942841581765</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>298.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -25720,7 +25720,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>283.4876499999776</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -25735,7 +25735,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>137.4664427423195</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -25787,7 +25787,7 @@
         <v>307.6316114025499</v>
       </c>
       <c r="N43" t="n">
-        <v>358.1850752716849</v>
+        <v>100.2142757831573</v>
       </c>
       <c r="O43" t="n">
         <v>427.445564079015</v>
@@ -25830,13 +25830,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>225.2103719673722</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>262.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>223.3391557398498</v>
       </c>
       <c r="E44" t="n">
         <v>217.3632896068686</v>
@@ -25845,10 +25845,10 @@
         <v>217.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>216.7573722870162</v>
+        <v>105.7203793077169</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>221.0096587035274</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25881,13 +25881,13 @@
         <v>63.87859882829446</v>
       </c>
       <c r="S44" t="n">
-        <v>307.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>462.2212965486107</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -25912,7 +25912,7 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>162.9639296649378</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -25960,7 +25960,7 @@
         <v>360.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>279.5639999646113</v>
+        <v>217.0764150531963</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -25972,7 +25972,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>245.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -26042,13 +26042,13 @@
         <v>175.3734797028554</v>
       </c>
       <c r="T46" t="n">
-        <v>23.02456650625771</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>12.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
         <v>39.37280983870968</v>
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2749653.217908312</v>
+        <v>2749653.217908311</v>
       </c>
     </row>
     <row r="6">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5865090.864871203</v>
+        <v>5865090.864871204</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6449606.77798226</v>
+        <v>6449606.777982263</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7094977.12754023</v>
+        <v>7094977.127540233</v>
       </c>
     </row>
     <row r="13">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8947668.987517329</v>
+        <v>8947668.987517327</v>
       </c>
     </row>
     <row r="16">
@@ -26284,7 +26284,7 @@
         <v>1435639.178444159</v>
       </c>
       <c r="G2" t="n">
-        <v>1493466.090910674</v>
+        <v>1493466.090910675</v>
       </c>
       <c r="H2" t="n">
         <v>1493466.090910675</v>
@@ -26293,22 +26293,22 @@
         <v>1493466.090910675</v>
       </c>
       <c r="J2" t="n">
+        <v>1363870.46392581</v>
+      </c>
+      <c r="K2" t="n">
         <v>1363870.463925811</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1363870.46392581</v>
       </c>
       <c r="L2" t="n">
         <v>1501883.201087887</v>
       </c>
       <c r="M2" t="n">
-        <v>1501883.201087888</v>
+        <v>1501883.201087886</v>
       </c>
       <c r="N2" t="n">
-        <v>1501883.201087886</v>
+        <v>1501883.201087887</v>
       </c>
       <c r="O2" t="n">
-        <v>1323162.218984811</v>
+        <v>1323162.21898481</v>
       </c>
       <c r="P2" t="n">
         <v>1234160.643232238</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>614247.5715792081</v>
+        <v>619095.9472656923</v>
       </c>
       <c r="C4" t="n">
-        <v>612495.6628399487</v>
+        <v>617344.0385264326</v>
       </c>
       <c r="D4" t="n">
-        <v>610741.3775271378</v>
+        <v>615589.7532136221</v>
       </c>
       <c r="E4" t="n">
-        <v>532123.6038252711</v>
+        <v>536922.2846154374</v>
       </c>
       <c r="F4" t="n">
-        <v>556398.2196192667</v>
+        <v>561196.9004094332</v>
       </c>
       <c r="G4" t="n">
-        <v>581187.6277435899</v>
+        <v>585986.3085337563</v>
       </c>
       <c r="H4" t="n">
-        <v>579514.6928034927</v>
+        <v>584313.3735936591</v>
       </c>
       <c r="I4" t="n">
-        <v>577839.422419066</v>
+        <v>582638.1032092323</v>
       </c>
       <c r="J4" t="n">
-        <v>520323.0592843113</v>
+        <v>524998.4738086244</v>
       </c>
       <c r="K4" t="n">
-        <v>518858.3176303694</v>
+        <v>523533.7321546826</v>
       </c>
       <c r="L4" t="n">
-        <v>581043.8351797319</v>
+        <v>585765.748114326</v>
       </c>
       <c r="M4" t="n">
-        <v>579313.7164781799</v>
+        <v>584035.6294127729</v>
       </c>
       <c r="N4" t="n">
-        <v>577581.1101536271</v>
+        <v>582303.0230882212</v>
       </c>
       <c r="O4" t="n">
-        <v>494869.5309141541</v>
+        <v>499544.9454384673</v>
       </c>
       <c r="P4" t="n">
-        <v>454063.7935190182</v>
+        <v>458739.2080433313</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>557983.7265393066</v>
+        <v>553135.3508528222</v>
       </c>
       <c r="C6" t="n">
-        <v>846263.635278566</v>
+        <v>841415.2595920819</v>
       </c>
       <c r="D6" t="n">
-        <v>848017.920591377</v>
+        <v>843169.5449048928</v>
       </c>
       <c r="E6" t="n">
-        <v>598855.2242285392</v>
+        <v>594056.5434383731</v>
       </c>
       <c r="F6" t="n">
-        <v>787848.4398248928</v>
+        <v>783049.7590347261</v>
       </c>
       <c r="G6" t="n">
-        <v>816932.0121670844</v>
+        <v>812133.3313769187</v>
       </c>
       <c r="H6" t="n">
-        <v>841004.9471071824</v>
+        <v>836206.2663170156</v>
       </c>
       <c r="I6" t="n">
-        <v>842680.2174916086</v>
+        <v>837881.5367014424</v>
       </c>
       <c r="J6" t="n">
-        <v>368737.4796414993</v>
+        <v>364062.0651171859</v>
       </c>
       <c r="K6" t="n">
-        <v>758298.2212954408</v>
+        <v>753622.806771128</v>
       </c>
       <c r="L6" t="n">
-        <v>774176.8869081549</v>
+        <v>769454.9739735613</v>
       </c>
       <c r="M6" t="n">
-        <v>851107.0056097079</v>
+        <v>846385.0926751136</v>
       </c>
       <c r="N6" t="n">
-        <v>852839.6119342588</v>
+        <v>848117.6989996657</v>
       </c>
       <c r="O6" t="n">
-        <v>688987.591070657</v>
+        <v>684312.1765463427</v>
       </c>
       <c r="P6" t="n">
-        <v>717377.5467132196</v>
+        <v>712702.1321889063</v>
       </c>
     </row>
   </sheetData>
@@ -26993,7 +26993,7 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>171</v>
@@ -27005,10 +27005,10 @@
         <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>93</v>
@@ -27439,22 +27439,22 @@
         <v>400</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E2" t="n">
         <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>56.51176829727014</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,16 +27481,16 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>400</v>
+        <v>157.3092074428799</v>
       </c>
       <c r="V2" t="n">
         <v>400</v>
@@ -27515,25 +27515,25 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>41.70910106771541</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.193089027603492</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27600,7 +27600,7 @@
         <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>367.9774060621958</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
         <v>400</v>
@@ -27609,10 +27609,10 @@
         <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>196.7485321638166</v>
       </c>
       <c r="J4" t="n">
         <v>35.26894883590776</v>
@@ -27670,10 +27670,10 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>56.51176829727081</v>
+      </c>
+      <c r="C5" t="n">
         <v>400</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>400</v>
@@ -27724,7 +27724,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
@@ -27739,7 +27739,7 @@
         <v>400</v>
       </c>
       <c r="Y5" t="n">
-        <v>56.51176829726995</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6">
@@ -27755,7 +27755,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>274.7686191606065</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27809,13 +27809,13 @@
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>326.8309322629039</v>
+        <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27837,7 +27837,7 @@
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>385.8774424048443</v>
+        <v>362.4974993401806</v>
       </c>
       <c r="F7" t="n">
         <v>400</v>
@@ -27846,7 +27846,7 @@
         <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
         <v>400</v>
@@ -27855,7 +27855,7 @@
         <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,25 +27879,25 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
+        <v>150.9583912744579</v>
+      </c>
+      <c r="V7" t="n">
         <v>400</v>
       </c>
-      <c r="V7" t="n">
-        <v>199.1703102162162</v>
-      </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27907,7 +27907,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>400</v>
@@ -27922,13 +27922,13 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>157.3092074428797</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27961,10 +27961,10 @@
         <v>400</v>
       </c>
       <c r="T8" t="n">
-        <v>307.3903671255644</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V8" t="n">
         <v>400</v>
@@ -27986,7 +27986,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
@@ -28034,13 +28034,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>342.2743756165772</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28052,10 +28052,10 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>326.2223250290382</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -28065,25 +28065,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
         <v>400</v>
@@ -28116,7 +28116,7 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>384.1335474495178</v>
       </c>
       <c r="T10" t="n">
         <v>400</v>
@@ -28125,13 +28125,13 @@
         <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>257.745553975398</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
         <v>287.4653528494624</v>
@@ -28247,7 +28247,7 @@
         <v>225</v>
       </c>
       <c r="J12" t="n">
-        <v>19.11687125883891</v>
+        <v>225</v>
       </c>
       <c r="K12" t="n">
         <v>225</v>
@@ -28262,7 +28262,7 @@
         <v>225</v>
       </c>
       <c r="O12" t="n">
-        <v>225</v>
+        <v>19.11687125883876</v>
       </c>
       <c r="P12" t="n">
         <v>225</v>
@@ -28481,31 +28481,31 @@
         <v>251</v>
       </c>
       <c r="I15" t="n">
-        <v>251</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J15" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>166.1982915220776</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>251</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="Q15" t="n">
-        <v>251</v>
+        <v>200.0719056307292</v>
       </c>
       <c r="R15" t="n">
         <v>251</v>
@@ -28721,22 +28721,22 @@
         <v>279</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>155.6705902671031</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>155.670590267103</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -28958,10 +28958,10 @@
         <v>279</v>
       </c>
       <c r="J21" t="n">
-        <v>155.6705902671031</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -28970,13 +28970,13 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>155.6705902671034</v>
       </c>
       <c r="Q21" t="n">
         <v>279</v>
@@ -29201,19 +29201,19 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>155.6705902671031</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>155.6705902671032</v>
+      </c>
+      <c r="P24" t="n">
         <v>279</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>279</v>
@@ -29432,13 +29432,13 @@
         <v>225</v>
       </c>
       <c r="J27" t="n">
-        <v>19.11687125883917</v>
+        <v>225</v>
       </c>
       <c r="K27" t="n">
         <v>225</v>
       </c>
       <c r="L27" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="M27" t="n">
         <v>225</v>
@@ -29666,10 +29666,10 @@
         <v>225</v>
       </c>
       <c r="I30" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J30" t="n">
-        <v>19.11687125883917</v>
+        <v>26.99048536749061</v>
       </c>
       <c r="K30" t="n">
         <v>225</v>
@@ -29803,7 +29803,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>291</v>
+        <v>282.5434086145858</v>
       </c>
       <c r="C32" t="n">
         <v>291</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>242.4220074428797</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S32" t="n">
         <v>291</v>
@@ -29909,25 +29909,25 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>127.8102101760009</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>9.889475266480218</v>
+      </c>
+      <c r="O33" t="n">
         <v>291</v>
       </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>173.0792650904796</v>
+        <v>291</v>
       </c>
       <c r="R33" t="n">
         <v>291</v>
@@ -29961,7 +29961,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>291</v>
+        <v>291.0000000000239</v>
       </c>
       <c r="C34" t="n">
         <v>291</v>
@@ -30061,7 +30061,7 @@
         <v>291</v>
       </c>
       <c r="I35" t="n">
-        <v>141.6245682972704</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30109,7 +30109,7 @@
         <v>291</v>
       </c>
       <c r="Y35" t="n">
-        <v>291</v>
+        <v>282.5434086145857</v>
       </c>
     </row>
     <row r="36">
@@ -30140,25 +30140,25 @@
         <v>291</v>
       </c>
       <c r="I36" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>291</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>227.0158611578289</v>
-      </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>9.88947526648019</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -30198,7 +30198,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>291.0000000000239</v>
+        <v>291</v>
       </c>
       <c r="C37" t="n">
         <v>291</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>250.8785988282945</v>
+        <v>242.4220074428797</v>
       </c>
       <c r="S38" t="n">
         <v>291</v>
@@ -30346,7 +30346,7 @@
         <v>291</v>
       </c>
       <c r="Y38" t="n">
-        <v>282.5434086145857</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39">
@@ -30380,7 +30380,7 @@
         <v>291</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -30395,13 +30395,13 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>227.0158611578287</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>291</v>
+        <v>227.0158611578291</v>
       </c>
       <c r="R39" t="n">
         <v>291</v>
@@ -30435,7 +30435,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>291</v>
+        <v>291.0000000000276</v>
       </c>
       <c r="C40" t="n">
         <v>291</v>
@@ -30629,13 +30629,13 @@
         <v>213</v>
       </c>
       <c r="N42" t="n">
-        <v>213</v>
+        <v>9.611785124016606</v>
       </c>
       <c r="O42" t="n">
         <v>213</v>
       </c>
       <c r="P42" t="n">
-        <v>158.5978143635411</v>
+        <v>213</v>
       </c>
       <c r="Q42" t="n">
         <v>213</v>
@@ -30693,10 +30693,10 @@
         <v>213</v>
       </c>
       <c r="I43" t="n">
-        <v>176.6334556201183</v>
+        <v>213</v>
       </c>
       <c r="J43" t="n">
-        <v>35.26894883590776</v>
+        <v>213</v>
       </c>
       <c r="K43" t="n">
         <v>213</v>
@@ -30726,10 +30726,10 @@
         <v>213</v>
       </c>
       <c r="T43" t="n">
-        <v>210.0245665062577</v>
+        <v>213</v>
       </c>
       <c r="U43" t="n">
-        <v>166.8643773812244</v>
+        <v>213</v>
       </c>
       <c r="V43" t="n">
         <v>213</v>
@@ -30857,7 +30857,7 @@
         <v>187</v>
       </c>
       <c r="K45" t="n">
-        <v>100.1207488653385</v>
+        <v>65.87389587248394</v>
       </c>
       <c r="L45" t="n">
         <v>187</v>
@@ -30875,7 +30875,7 @@
         <v>187</v>
       </c>
       <c r="Q45" t="n">
-        <v>173.0792650904796</v>
+        <v>187</v>
       </c>
       <c r="R45" t="n">
         <v>187</v>
@@ -30933,7 +30933,7 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J46" t="n">
-        <v>35.26894883590776</v>
+        <v>71.17842411646478</v>
       </c>
       <c r="K46" t="n">
         <v>187</v>
@@ -34746,7 +34746,7 @@
         <v>814</v>
       </c>
       <c r="K2" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>814</v>
@@ -34886,7 +34886,7 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>86.99650122523923</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
         <v>125.6171440322581</v>
@@ -34895,10 +34895,10 @@
         <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>223.3665443798817</v>
+        <v>20.11507654369831</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -34983,10 +34983,10 @@
         <v>814</v>
       </c>
       <c r="K5" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M5" t="n">
         <v>814</v>
@@ -35123,7 +35123,7 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>104.8965375678877</v>
+        <v>81.5165945032241</v>
       </c>
       <c r="F7" t="n">
         <v>125.6171440322581</v>
@@ -35132,7 +35132,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
         <v>223.3665443798817</v>
@@ -35141,7 +35141,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35351,25 +35351,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
         <v>223.3665443798817</v>
@@ -35402,7 +35402,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>37.62652029714457</v>
+        <v>21.7600677466624</v>
       </c>
       <c r="T10" t="n">
         <v>189.9754334937423</v>
@@ -35411,13 +35411,13 @@
         <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
-        <v>58.57524375918177</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -35457,7 +35457,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230993</v>
+        <v>240.811073919941</v>
       </c>
       <c r="L11" t="n">
         <v>814</v>
@@ -35466,16 +35466,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>161.5508809199775</v>
+        <v>814</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35533,7 +35533,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J12" t="n">
-        <v>144.3254774965146</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K12" t="n">
         <v>416.1038546407913</v>
@@ -35548,7 +35548,7 @@
         <v>359.6265501086548</v>
       </c>
       <c r="O12" t="n">
-        <v>466.4570219027464</v>
+        <v>260.5738931615851</v>
       </c>
       <c r="P12" t="n">
         <v>338.6660045146532</v>
@@ -35691,10 +35691,10 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>113.7832223189554</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230993</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -35712,7 +35712,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>161.5508809199775</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35767,31 +35767,31 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>33.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>376.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K15" t="n">
-        <v>442.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>440.2896668707646</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M15" t="n">
         <v>337.9500421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>134.6265501086548</v>
+        <v>385.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>241.4570219027464</v>
+        <v>492.4570219027464</v>
       </c>
       <c r="P15" t="n">
-        <v>113.6660045146532</v>
+        <v>364.6660045146532</v>
       </c>
       <c r="Q15" t="n">
-        <v>77.92073490952041</v>
+        <v>26.99264054024963</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35931,10 +35931,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>435.3966095009885</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
@@ -35943,10 +35943,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>435.3966095009885</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>443.0293889420883</v>
@@ -36007,22 +36007,22 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J18" t="n">
-        <v>125.2086062376757</v>
+        <v>280.8791965047788</v>
       </c>
       <c r="K18" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L18" t="n">
-        <v>429.76196561579</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M18" t="n">
-        <v>86.95004216450428</v>
+        <v>365.9500421645043</v>
       </c>
       <c r="N18" t="n">
         <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
-        <v>520.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P18" t="n">
         <v>113.6660045146532</v>
@@ -36168,10 +36168,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230993</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>532.5214919778891</v>
+        <v>814</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
@@ -36180,13 +36180,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>443.0293889420883</v>
+        <v>64.42599844307681</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36244,10 +36244,10 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J21" t="n">
-        <v>280.8791965047788</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K21" t="n">
-        <v>191.1038546407913</v>
+        <v>470.1038546407913</v>
       </c>
       <c r="L21" t="n">
         <v>274.091375348687</v>
@@ -36256,13 +36256,13 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N21" t="n">
-        <v>413.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O21" t="n">
         <v>241.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>113.6660045146532</v>
+        <v>269.3365947817566</v>
       </c>
       <c r="Q21" t="n">
         <v>105.9207349095204</v>
@@ -36402,13 +36402,13 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>113.7832223189554</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>435.3966095009885</v>
       </c>
       <c r="L23" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
@@ -36417,7 +36417,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -36487,19 +36487,19 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L24" t="n">
-        <v>429.7619656157901</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M24" t="n">
-        <v>365.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N24" t="n">
         <v>134.6265501086548</v>
       </c>
       <c r="O24" t="n">
-        <v>241.4570219027464</v>
+        <v>397.1276121698496</v>
       </c>
       <c r="P24" t="n">
-        <v>113.6660045146532</v>
+        <v>392.6660045146532</v>
       </c>
       <c r="Q24" t="n">
         <v>105.9207349095204</v>
@@ -36642,22 +36642,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>314.0531751575267</v>
       </c>
       <c r="L26" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>216.5925220534073</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>773.0000000000275</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36718,13 +36718,13 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J27" t="n">
-        <v>144.3254774965148</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K27" t="n">
         <v>416.1038546407913</v>
       </c>
       <c r="L27" t="n">
-        <v>499.091375348687</v>
+        <v>293.2082466075261</v>
       </c>
       <c r="M27" t="n">
         <v>311.9500421645043</v>
@@ -36876,22 +36876,22 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>772.9999999999999</v>
+        <v>314.0531751575193</v>
       </c>
       <c r="M29" t="n">
-        <v>508.4487058835364</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>773.0000000000348</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -36952,10 +36952,10 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>144.3254774965148</v>
+        <v>152.1990916051663</v>
       </c>
       <c r="K30" t="n">
         <v>416.1038546407913</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="K32" t="n">
-        <v>727.10793207605</v>
+        <v>727.1079320763188</v>
       </c>
       <c r="L32" t="n">
-        <v>773.0000000000001</v>
+        <v>773</v>
       </c>
       <c r="M32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="N32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="O32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="P32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="Q32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37195,25 +37195,25 @@
         <v>125.2086062376757</v>
       </c>
       <c r="K33" t="n">
-        <v>318.9140648167922</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L33" t="n">
-        <v>565.0913753486871</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M33" t="n">
         <v>86.95004216450428</v>
       </c>
       <c r="N33" t="n">
-        <v>134.6265501086548</v>
+        <v>144.516025375135</v>
       </c>
       <c r="O33" t="n">
-        <v>241.4570219027464</v>
+        <v>532.4570219027464</v>
       </c>
       <c r="P33" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>117.9207349095204</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37247,7 +37247,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.886199662921342</v>
+        <v>3.886199662945266</v>
       </c>
       <c r="C34" t="n">
         <v>18.27475335195533</v>
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="K35" t="n">
-        <v>727.1079320762854</v>
+        <v>773</v>
       </c>
       <c r="L35" t="n">
-        <v>773</v>
+        <v>727.1079320760183</v>
       </c>
       <c r="M35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="N35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="O35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="P35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="Q35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37426,7 +37426,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>73.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>125.2086062376757</v>
@@ -37438,13 +37438,13 @@
         <v>274.091375348687</v>
       </c>
       <c r="M36" t="n">
-        <v>313.9659033223331</v>
+        <v>377.9500421645043</v>
       </c>
       <c r="N36" t="n">
         <v>134.6265501086548</v>
       </c>
       <c r="O36" t="n">
-        <v>241.4570219027464</v>
+        <v>251.3464971692266</v>
       </c>
       <c r="P36" t="n">
         <v>113.6660045146532</v>
@@ -37484,7 +37484,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.886199662945266</v>
+        <v>3.886199662921342</v>
       </c>
       <c r="C37" t="n">
         <v>18.27475335195533</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="K38" t="n">
-        <v>727.1079320759661</v>
+        <v>727.1079320762573</v>
       </c>
       <c r="L38" t="n">
         <v>773</v>
       </c>
       <c r="M38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="N38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="O38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="P38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="Q38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37666,7 +37666,7 @@
         <v>73.87361410865147</v>
       </c>
       <c r="J39" t="n">
-        <v>125.2086062376757</v>
+        <v>416.2086062376757</v>
       </c>
       <c r="K39" t="n">
         <v>191.1038546407913</v>
@@ -37681,13 +37681,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O39" t="n">
-        <v>468.4728830605751</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P39" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q39" t="n">
-        <v>117.9207349095204</v>
+        <v>53.93659606734953</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37721,7 +37721,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.886199662921342</v>
+        <v>3.886199662948904</v>
       </c>
       <c r="C40" t="n">
         <v>18.27475335195533</v>
@@ -37824,13 +37824,13 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>314.0531751574904</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
@@ -37839,10 +37839,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O41" t="n">
-        <v>709.3149054985574</v>
+        <v>773.0000000000639</v>
       </c>
       <c r="P41" t="n">
-        <v>773.000000000063</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>443.0293889420883</v>
@@ -37915,13 +37915,13 @@
         <v>299.9500421645043</v>
       </c>
       <c r="N42" t="n">
-        <v>347.6265501086548</v>
+        <v>144.2383352326714</v>
       </c>
       <c r="O42" t="n">
         <v>454.4570219027464</v>
       </c>
       <c r="P42" t="n">
-        <v>272.2638188781943</v>
+        <v>326.6660045146532</v>
       </c>
       <c r="Q42" t="n">
         <v>39.92073490952041</v>
@@ -37979,10 +37979,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>36.36654437988173</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>177.7310511640922</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38012,10 +38012,10 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.975433493742287</v>
       </c>
       <c r="U43" t="n">
-        <v>15.90598610676645</v>
+        <v>62.04160872554206</v>
       </c>
       <c r="V43" t="n">
         <v>13.82968978378381</v>
@@ -38061,28 +38061,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>772.9999999999999</v>
+        <v>773</v>
       </c>
       <c r="M44" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O44" t="n">
-        <v>435.4691769176098</v>
+        <v>113.18697554247</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38143,7 +38143,7 @@
         <v>312.2086062376757</v>
       </c>
       <c r="K45" t="n">
-        <v>291.2246035061298</v>
+        <v>256.9777505132753</v>
       </c>
       <c r="L45" t="n">
         <v>461.091375348687</v>
@@ -38161,7 +38161,7 @@
         <v>300.6660045146532</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>13.92073490952041</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -38219,7 +38219,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>35.909475280557</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
